--- a/jogos_2025-04-07.xlsx
+++ b/jogos_2025-04-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="279">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -280,24 +226,24 @@
     <t>Czech Republic FNL</t>
   </si>
   <si>
+    <t>Israel Liga Leumit</t>
+  </si>
+  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
-    <t>Israel Liga Leumit</t>
+    <t>Turkey Süper Lig</t>
+  </si>
+  <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Israel Israeli Premier League</t>
   </si>
   <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
-    <t>Israel Israeli Premier League</t>
-  </si>
-  <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Turkey Süper Lig</t>
-  </si>
-  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
@@ -307,33 +253,33 @@
     <t>Portugal Liga NOS</t>
   </si>
   <si>
+    <t>Hungary NB II</t>
+  </si>
+  <si>
     <t>Netherlands Eerste Divisie</t>
   </si>
   <si>
-    <t>Hungary NB II</t>
-  </si>
-  <si>
     <t>Iceland Úrvalsdeild</t>
   </si>
   <si>
+    <t>Argentina Primera División</t>
+  </si>
+  <si>
+    <t>Spain Segunda División</t>
+  </si>
+  <si>
+    <t>Italy Serie C Group C</t>
+  </si>
+  <si>
     <t>Italy Serie C Group A</t>
   </si>
   <si>
-    <t>Argentina Primera División</t>
-  </si>
-  <si>
-    <t>Spain Segunda División</t>
-  </si>
-  <si>
-    <t>Italy Serie C Group C</t>
+    <t>France Ligue 2</t>
   </si>
   <si>
     <t>Italy Serie A</t>
   </si>
   <si>
-    <t>France Ligue 2</t>
-  </si>
-  <si>
     <t>England Premier League</t>
   </si>
   <si>
@@ -343,12 +289,12 @@
     <t>Argentina Prim B Nacional</t>
   </si>
   <si>
+    <t>Jamaica Jamaica National Premier League</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Jamaica Jamaica National Premier League</t>
-  </si>
-  <si>
     <t>Uruguay Primera División</t>
   </si>
   <si>
@@ -370,19 +316,34 @@
     <t>Al Jazira</t>
   </si>
   <si>
+    <t>SSC Farul</t>
+  </si>
+  <si>
     <t>Lokomotiv Plovdiv</t>
   </si>
   <si>
-    <t>SSC Farul</t>
-  </si>
-  <si>
     <t>Atromitos</t>
   </si>
   <si>
+    <t>Baník Ostrava U21</t>
+  </si>
+  <si>
     <t>Polessya</t>
   </si>
   <si>
-    <t>Baník Ostrava U21</t>
+    <t>Hapoel Petah Tikva</t>
+  </si>
+  <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>Novi Pazar</t>
+  </si>
+  <si>
+    <t>Mladost Lučani</t>
+  </si>
+  <si>
+    <t>Hapoel Kfar Shalem</t>
   </si>
   <si>
     <t>Čukarički</t>
@@ -391,48 +352,33 @@
     <t>Bačka Topola</t>
   </si>
   <si>
-    <t>Novi Pazar</t>
-  </si>
-  <si>
-    <t>Hapoel Petah Tikva</t>
-  </si>
-  <si>
-    <t>Mladost Lučani</t>
-  </si>
-  <si>
-    <t>Hapoel Kfar Shalem</t>
-  </si>
-  <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
     <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
+    <t>Kasımpaşa</t>
+  </si>
+  <si>
+    <t>Varberg</t>
+  </si>
+  <si>
+    <t>Hapoel Hadera</t>
+  </si>
+  <si>
+    <t>Göztepe</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
     <t>Brøndby</t>
   </si>
   <si>
-    <t>Hapoel Hadera</t>
-  </si>
-  <si>
-    <t>Varberg</t>
-  </si>
-  <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>Göztepe</t>
-  </si>
-  <si>
-    <t>Kasımpaşa</t>
-  </si>
-  <si>
     <t>Puszcza Niepołomice</t>
   </si>
   <si>
-    <t>CSKA 1948 Sofia</t>
-  </si>
-  <si>
     <t>Malmö FF</t>
   </si>
   <si>
@@ -445,39 +391,39 @@
     <t>Farense</t>
   </si>
   <si>
+    <t>Mezőkövesd-Zsóry</t>
+  </si>
+  <si>
+    <t>Utrecht II</t>
+  </si>
+  <si>
     <t>AZ II</t>
   </si>
   <si>
-    <t>Mezőkövesd-Zsóry</t>
-  </si>
-  <si>
-    <t>Utrecht II</t>
-  </si>
-  <si>
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
+    <t>Deportivo Riestra</t>
+  </si>
+  <si>
+    <t>Elche CF</t>
+  </si>
+  <si>
+    <t>SSC Giugliano</t>
+  </si>
+  <si>
+    <t>AlbinoLeffe</t>
+  </si>
+  <si>
     <t>Calcio Padova</t>
   </si>
   <si>
-    <t>Deportivo Riestra</t>
-  </si>
-  <si>
-    <t>Elche CF</t>
-  </si>
-  <si>
-    <t>AlbinoLeffe</t>
-  </si>
-  <si>
-    <t>SSC Giugliano</t>
+    <t>Dunkerque</t>
   </si>
   <si>
     <t>Bologna</t>
   </si>
   <si>
-    <t>Dunkerque</t>
-  </si>
-  <si>
     <t>Leicester City</t>
   </si>
   <si>
@@ -496,12 +442,12 @@
     <t>Agropecuario</t>
   </si>
   <si>
+    <t>Racing United</t>
+  </si>
+  <si>
     <t>Atlético GO</t>
   </si>
   <si>
-    <t>Racing United</t>
-  </si>
-  <si>
     <t>Ferro Carril Oeste</t>
   </si>
   <si>
@@ -511,12 +457,12 @@
     <t>Patronato</t>
   </si>
   <si>
+    <t>Atlético Tucumán</t>
+  </si>
+  <si>
     <t>Tigre</t>
   </si>
   <si>
-    <t>Atlético Tucumán</t>
-  </si>
-  <si>
     <t>Quilmes</t>
   </si>
   <si>
@@ -535,19 +481,34 @@
     <t>Al Wasl</t>
   </si>
   <si>
+    <t>Unirea Slobozia</t>
+  </si>
+  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
-    <t>Unirea Slobozia</t>
-  </si>
-  <si>
     <t>Asteras Tripolis</t>
   </si>
   <si>
+    <t>Sigma Olomouc II</t>
+  </si>
+  <si>
     <t>Karpaty</t>
   </si>
   <si>
-    <t>Sigma Olomouc II</t>
+    <t>Hapoel Kfar Saba</t>
+  </si>
+  <si>
+    <t>Bnei Yehuda</t>
+  </si>
+  <si>
+    <t>Radnički Niš</t>
+  </si>
+  <si>
+    <t>Vojvodina</t>
+  </si>
+  <si>
+    <t>Maccabi Herzliya</t>
   </si>
   <si>
     <t>IMT Novi Beograd</t>
@@ -556,48 +517,33 @@
     <t>Železničar Pančevo</t>
   </si>
   <si>
-    <t>Radnički Niš</t>
-  </si>
-  <si>
-    <t>Hapoel Kfar Saba</t>
-  </si>
-  <si>
-    <t>Vojvodina</t>
-  </si>
-  <si>
-    <t>Maccabi Herzliya</t>
-  </si>
-  <si>
-    <t>Bnei Yehuda</t>
-  </si>
-  <si>
     <t>Al Ain</t>
   </si>
   <si>
+    <t>Ludogorets</t>
+  </si>
+  <si>
+    <t>Beşiktaş</t>
+  </si>
+  <si>
+    <t>Örebro</t>
+  </si>
+  <si>
+    <t>Bnei Sakhnin</t>
+  </si>
+  <si>
+    <t>Gazişehir Gaziantep</t>
+  </si>
+  <si>
+    <t>Falkenberg</t>
+  </si>
+  <si>
     <t>AGF</t>
   </si>
   <si>
-    <t>Bnei Sakhnin</t>
-  </si>
-  <si>
-    <t>Örebro</t>
-  </si>
-  <si>
-    <t>Falkenberg</t>
-  </si>
-  <si>
-    <t>Gazişehir Gaziantep</t>
-  </si>
-  <si>
-    <t>Beşiktaş</t>
-  </si>
-  <si>
     <t>Raków Częstochowa</t>
   </si>
   <si>
-    <t>Ludogorets</t>
-  </si>
-  <si>
     <t>Elfsborg</t>
   </si>
   <si>
@@ -610,39 +556,39 @@
     <t>Casa Pia</t>
   </si>
   <si>
+    <t>Vasas</t>
+  </si>
+  <si>
+    <t>ADO Den Haag</t>
+  </si>
+  <si>
     <t>PSV II</t>
   </si>
   <si>
-    <t>Vasas</t>
-  </si>
-  <si>
-    <t>ADO Den Haag</t>
-  </si>
-  <si>
     <t>ÍBV</t>
   </si>
   <si>
+    <t>Platense</t>
+  </si>
+  <si>
+    <t>Racing Club de Ferrol</t>
+  </si>
+  <si>
+    <t>Casertana</t>
+  </si>
+  <si>
+    <t>Pro Vercelli</t>
+  </si>
+  <si>
     <t>Lecco</t>
   </si>
   <si>
-    <t>Platense</t>
-  </si>
-  <si>
-    <t>Racing Club de Ferrol</t>
-  </si>
-  <si>
-    <t>Pro Vercelli</t>
-  </si>
-  <si>
-    <t>Casertana</t>
+    <t>Guingamp</t>
   </si>
   <si>
     <t>Napoli</t>
   </si>
   <si>
-    <t>Guingamp</t>
-  </si>
-  <si>
     <t>Newcastle United</t>
   </si>
   <si>
@@ -661,12 +607,12 @@
     <t>Colón</t>
   </si>
   <si>
+    <t>Chapelton</t>
+  </si>
+  <si>
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>Chapelton</t>
-  </si>
-  <si>
     <t>Arsenal de Sarandí</t>
   </si>
   <si>
@@ -676,12 +622,12 @@
     <t>All Boys</t>
   </si>
   <si>
+    <t>Instituto</t>
+  </si>
+  <si>
     <t>Newell's Old Boys</t>
   </si>
   <si>
-    <t>Instituto</t>
-  </si>
-  <si>
     <t>Racing Córdoba</t>
   </si>
   <si>
@@ -697,87 +643,87 @@
     <t>[]</t>
   </si>
   <si>
+    <t>['42']</t>
+  </si>
+  <si>
     <t>['66']</t>
   </si>
   <si>
-    <t>['42']</t>
+    <t>['52', '74', '81']</t>
   </si>
   <si>
     <t>['88']</t>
   </si>
   <si>
-    <t>['52', '74', '81']</t>
+    <t>['35']</t>
+  </si>
+  <si>
+    <t>['2', '13', '45+3']</t>
+  </si>
+  <si>
+    <t>['14', '60', '73']</t>
+  </si>
+  <si>
+    <t>['50']</t>
   </si>
   <si>
     <t>['32']</t>
   </si>
   <si>
-    <t>['14', '60', '73']</t>
-  </si>
-  <si>
-    <t>['35']</t>
-  </si>
-  <si>
-    <t>['50']</t>
-  </si>
-  <si>
-    <t>['2', '13', '45+3']</t>
+    <t>['90+1']</t>
+  </si>
+  <si>
+    <t>['14']</t>
+  </si>
+  <si>
+    <t>['15', '90+3']</t>
+  </si>
+  <si>
+    <t>['90+4']</t>
   </si>
   <si>
     <t>['13', '50']</t>
   </si>
   <si>
-    <t>['15', '90+3']</t>
-  </si>
-  <si>
-    <t>['90+4']</t>
-  </si>
-  <si>
-    <t>['14']</t>
-  </si>
-  <si>
-    <t>['90+1']</t>
-  </si>
-  <si>
     <t>['47', '78']</t>
   </si>
   <si>
     <t>['22', '44']</t>
   </si>
   <si>
+    <t>['31', '41', '62']</t>
+  </si>
+  <si>
+    <t>['40']</t>
+  </si>
+  <si>
     <t>['52', '56']</t>
   </si>
   <si>
-    <t>['31', '41', '62']</t>
-  </si>
-  <si>
-    <t>['40']</t>
-  </si>
-  <si>
     <t>['49', '79']</t>
   </si>
   <si>
+    <t>['57']</t>
+  </si>
+  <si>
+    <t>['38']</t>
+  </si>
+  <si>
+    <t>['28']</t>
+  </si>
+  <si>
+    <t>['5', '11', '52']</t>
+  </si>
+  <si>
     <t>['2', '11']</t>
   </si>
   <si>
-    <t>['57']</t>
-  </si>
-  <si>
-    <t>['38']</t>
-  </si>
-  <si>
-    <t>['5', '11', '52']</t>
-  </si>
-  <si>
-    <t>['28']</t>
+    <t>['69', '82', '90+7']</t>
   </si>
   <si>
     <t>['64']</t>
   </si>
   <si>
-    <t>['69', '82', '90+7']</t>
-  </si>
-  <si>
     <t>['87']</t>
   </si>
   <si>
@@ -790,12 +736,12 @@
     <t>['55', '90+1']</t>
   </si>
   <si>
+    <t>['31', '47', '80']</t>
+  </si>
+  <si>
     <t>['43', '69', '79', '90+3']</t>
   </si>
   <si>
-    <t>['31', '47', '80']</t>
-  </si>
-  <si>
     <t>['41', '44']</t>
   </si>
   <si>
@@ -820,69 +766,69 @@
     <t>['7', '45+2', '64', '73', '81']</t>
   </si>
   <si>
+    <t>['71']</t>
+  </si>
+  <si>
     <t>['7', '32']</t>
   </si>
   <si>
-    <t>['71']</t>
-  </si>
-  <si>
     <t>['60']</t>
   </si>
   <si>
+    <t>['45+7', '68', '90+4']</t>
+  </si>
+  <si>
+    <t>['21', '33', '90+2']</t>
+  </si>
+  <si>
+    <t>['12', '71']</t>
+  </si>
+  <si>
     <t>['38', '76']</t>
   </si>
   <si>
-    <t>['45+7', '68', '90+4']</t>
-  </si>
-  <si>
-    <t>['21', '33', '90+2']</t>
-  </si>
-  <si>
-    <t>['12', '71']</t>
+    <t>['39', '82', '90+5']</t>
+  </si>
+  <si>
+    <t>['90']</t>
+  </si>
+  <si>
+    <t>['29']</t>
+  </si>
+  <si>
+    <t>['48']</t>
+  </si>
+  <si>
+    <t>['17', '82']</t>
   </si>
   <si>
     <t>['73']</t>
   </si>
   <si>
-    <t>['29']</t>
-  </si>
-  <si>
-    <t>['17', '82']</t>
-  </si>
-  <si>
-    <t>['48']</t>
-  </si>
-  <si>
-    <t>['90']</t>
-  </si>
-  <si>
-    <t>['39', '82', '90+5']</t>
-  </si>
-  <si>
     <t>['52', '86', '90+9']</t>
   </si>
   <si>
+    <t>['58']</t>
+  </si>
+  <si>
     <t>['14', '72']</t>
   </si>
   <si>
-    <t>['58']</t>
+    <t>['11']</t>
+  </si>
+  <si>
+    <t>['37']</t>
   </si>
   <si>
     <t>['78']</t>
   </si>
   <si>
-    <t>['37']</t>
-  </si>
-  <si>
-    <t>['11']</t>
+    <t>['90+6']</t>
   </si>
   <si>
     <t>['18']</t>
   </si>
   <si>
-    <t>['90+6']</t>
-  </si>
-  <si>
     <t>['2', '11', '34']</t>
   </si>
   <si>
@@ -901,10 +847,10 @@
     <t>['47']</t>
   </si>
   <si>
+    <t>['56', '81']</t>
+  </si>
+  <si>
     <t>['13', '74']</t>
-  </si>
-  <si>
-    <t>['56', '81']</t>
   </si>
 </sst>
 </file>
@@ -1268,10 +1214,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD56"/>
+  <dimension ref="A1:AL56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1386,79 +1332,25 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45754</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="F2" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1473,7 +1365,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L2">
         <v>3.83</v>
@@ -1548,87 +1440,33 @@
         <v>1.03</v>
       </c>
       <c r="AJ2" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="AK2" t="s">
-        <v>264</v>
-      </c>
-      <c r="AL2">
-        <v>2.25</v>
-      </c>
-      <c r="AM2">
-        <v>1.18</v>
-      </c>
-      <c r="AN2">
-        <v>1.14</v>
-      </c>
-      <c r="AO2">
-        <v>6</v>
-      </c>
-      <c r="AP2">
-        <v>1.5</v>
-      </c>
-      <c r="AQ2">
-        <v>1.85</v>
-      </c>
-      <c r="AR2">
-        <v>2.34</v>
-      </c>
-      <c r="AS2">
-        <v>3.2</v>
-      </c>
-      <c r="AT2">
-        <v>4.3</v>
-      </c>
-      <c r="AU2">
-        <v>2.35</v>
-      </c>
-      <c r="AV2">
-        <v>1.91</v>
-      </c>
-      <c r="AW2">
-        <v>1.5</v>
-      </c>
-      <c r="AX2">
-        <v>1.26</v>
-      </c>
-      <c r="AY2">
-        <v>1.18</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>3.4</v>
-      </c>
-      <c r="BC2">
-        <v>1.4</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>246</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45754.33333333334</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45754</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="F3" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1643,7 +1481,7 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L3">
         <v>3.26</v>
@@ -1718,87 +1556,33 @@
         <v>1.04</v>
       </c>
       <c r="AJ3" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="AK3" t="s">
-        <v>265</v>
-      </c>
-      <c r="AL3">
-        <v>1.92</v>
-      </c>
-      <c r="AM3">
-        <v>1.3</v>
-      </c>
-      <c r="AN3">
-        <v>1.21</v>
-      </c>
-      <c r="AO3">
-        <v>12</v>
-      </c>
-      <c r="AP3">
-        <v>1.35</v>
-      </c>
-      <c r="AQ3">
-        <v>1.6</v>
-      </c>
-      <c r="AR3">
-        <v>1.98</v>
-      </c>
-      <c r="AS3">
-        <v>2.5</v>
-      </c>
-      <c r="AT3">
-        <v>3.3</v>
-      </c>
-      <c r="AU3">
-        <v>2.9</v>
-      </c>
-      <c r="AV3">
-        <v>2.17</v>
-      </c>
-      <c r="AW3">
-        <v>1.74</v>
-      </c>
-      <c r="AX3">
-        <v>1.46</v>
-      </c>
-      <c r="AY3">
-        <v>1.28</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>2.75</v>
-      </c>
-      <c r="BC3">
-        <v>1.57</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>247</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45754.375</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45754</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="F4" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1813,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L4">
         <v>2.29</v>
@@ -1888,87 +1672,33 @@
         <v>1.03</v>
       </c>
       <c r="AJ4" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="AK4" t="s">
-        <v>266</v>
-      </c>
-      <c r="AL4">
-        <v>1.32</v>
-      </c>
-      <c r="AM4">
-        <v>1.36</v>
-      </c>
-      <c r="AN4">
-        <v>1.6</v>
-      </c>
-      <c r="AO4">
-        <v>10</v>
-      </c>
-      <c r="AP4">
-        <v>1.5</v>
-      </c>
-      <c r="AQ4">
-        <v>1.87</v>
-      </c>
-      <c r="AR4">
-        <v>2.4</v>
-      </c>
-      <c r="AS4">
-        <v>3.25</v>
-      </c>
-      <c r="AT4">
-        <v>4.7</v>
-      </c>
-      <c r="AU4">
-        <v>2.45</v>
-      </c>
-      <c r="AV4">
-        <v>1.87</v>
-      </c>
-      <c r="AW4">
-        <v>1.5</v>
-      </c>
-      <c r="AX4">
-        <v>1.3</v>
-      </c>
-      <c r="AY4">
-        <v>1.18</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>1.85</v>
-      </c>
-      <c r="BC4">
-        <v>2.38</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>248</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45754.39583333334</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45754</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="F5" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1983,7 +1713,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L5">
         <v>2.35</v>
@@ -2058,427 +1788,265 @@
         <v>1.15</v>
       </c>
       <c r="AJ5" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="AK5" t="s">
-        <v>267</v>
-      </c>
-      <c r="AL5">
-        <v>1.45</v>
-      </c>
-      <c r="AM5">
-        <v>1.25</v>
-      </c>
-      <c r="AN5">
-        <v>1.5</v>
-      </c>
-      <c r="AO5">
-        <v>4</v>
-      </c>
-      <c r="AP5">
-        <v>1.25</v>
-      </c>
-      <c r="AQ5">
-        <v>1.46</v>
-      </c>
-      <c r="AR5">
-        <v>1.77</v>
-      </c>
-      <c r="AS5">
-        <v>2.22</v>
-      </c>
-      <c r="AT5">
-        <v>2.85</v>
-      </c>
-      <c r="AU5">
-        <v>3.5</v>
-      </c>
-      <c r="AV5">
-        <v>2.5</v>
-      </c>
-      <c r="AW5">
-        <v>1.94</v>
-      </c>
-      <c r="AX5">
-        <v>1.59</v>
-      </c>
-      <c r="AY5">
-        <v>1.37</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>1.8</v>
-      </c>
-      <c r="BC5">
-        <v>2.05</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>249</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45754.45138888889</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45754</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="F6" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>206</v>
+      </c>
+      <c r="L6">
+        <v>1.71</v>
+      </c>
+      <c r="M6">
+        <v>3.55</v>
+      </c>
+      <c r="N6">
+        <v>4.9</v>
+      </c>
+      <c r="O6">
+        <v>1.47</v>
+      </c>
+      <c r="P6">
+        <v>7.8</v>
+      </c>
+      <c r="Q6">
+        <v>3.1</v>
+      </c>
+      <c r="R6">
+        <v>1.41</v>
+      </c>
+      <c r="S6">
+        <v>2.81</v>
+      </c>
+      <c r="T6">
+        <v>3.08</v>
+      </c>
+      <c r="U6">
+        <v>1.35</v>
+      </c>
+      <c r="V6">
+        <v>7.5</v>
+      </c>
+      <c r="W6">
+        <v>1.03</v>
+      </c>
+      <c r="X6">
+        <v>1.03</v>
+      </c>
+      <c r="Y6">
+        <v>9</v>
+      </c>
+      <c r="Z6">
+        <v>1.29</v>
+      </c>
+      <c r="AA6">
+        <v>3.3</v>
+      </c>
+      <c r="AB6">
         <v>2</v>
       </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6" t="s">
-        <v>224</v>
-      </c>
-      <c r="L6">
-        <v>2.14</v>
-      </c>
-      <c r="M6">
-        <v>3.41</v>
-      </c>
-      <c r="N6">
-        <v>3.23</v>
-      </c>
-      <c r="O6">
-        <v>1.83</v>
-      </c>
-      <c r="P6">
-        <v>8.5</v>
-      </c>
-      <c r="Q6">
-        <v>2.25</v>
-      </c>
-      <c r="R6">
-        <v>1.5</v>
-      </c>
-      <c r="S6">
-        <v>2.5</v>
-      </c>
-      <c r="T6">
-        <v>3.5</v>
-      </c>
-      <c r="U6">
-        <v>1.29</v>
-      </c>
-      <c r="V6">
-        <v>11</v>
-      </c>
-      <c r="W6">
-        <v>1.05</v>
-      </c>
-      <c r="X6">
-        <v>1.01</v>
-      </c>
-      <c r="Y6">
-        <v>8.5</v>
-      </c>
-      <c r="Z6">
-        <v>1.36</v>
-      </c>
-      <c r="AA6">
-        <v>2.99</v>
-      </c>
-      <c r="AB6">
-        <v>2.1</v>
-      </c>
       <c r="AC6">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AD6">
-        <v>3.87</v>
+        <v>3.6</v>
       </c>
       <c r="AE6">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF6">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AG6">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH6">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AI6">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AJ6" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="AK6" t="s">
-        <v>268</v>
-      </c>
-      <c r="AL6">
-        <v>1.35</v>
-      </c>
-      <c r="AM6">
-        <v>1.34</v>
-      </c>
-      <c r="AN6">
-        <v>1.57</v>
-      </c>
-      <c r="AO6">
-        <v>10</v>
-      </c>
-      <c r="AP6">
-        <v>1.56</v>
-      </c>
-      <c r="AQ6">
-        <v>1.95</v>
-      </c>
-      <c r="AR6">
-        <v>2.55</v>
-      </c>
-      <c r="AS6">
-        <v>3.3</v>
-      </c>
-      <c r="AT6">
-        <v>4.5</v>
-      </c>
-      <c r="AU6">
-        <v>2.23</v>
-      </c>
-      <c r="AV6">
-        <v>1.75</v>
-      </c>
-      <c r="AW6">
-        <v>1.45</v>
-      </c>
-      <c r="AX6">
-        <v>1.27</v>
-      </c>
-      <c r="AY6">
-        <v>1.16</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>1.83</v>
-      </c>
-      <c r="BC6">
-        <v>2.25</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>250</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45754.47916666666</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45754</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="G7">
         <v>1</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L7">
-        <v>1.71</v>
+        <v>2.14</v>
       </c>
       <c r="M7">
-        <v>3.55</v>
+        <v>3.41</v>
       </c>
       <c r="N7">
-        <v>4.9</v>
+        <v>3.23</v>
       </c>
       <c r="O7">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="P7">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="Q7">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="R7">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S7">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="T7">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="U7">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="V7">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="W7">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z7">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AA7">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="AB7">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC7">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AD7">
-        <v>3.6</v>
+        <v>3.87</v>
       </c>
       <c r="AE7">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF7">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AG7">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH7">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AI7">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AJ7" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="AK7" t="s">
-        <v>269</v>
-      </c>
-      <c r="AL7">
-        <v>1.12</v>
-      </c>
-      <c r="AM7">
-        <v>1.25</v>
-      </c>
-      <c r="AN7">
-        <v>2.32</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>1.3</v>
-      </c>
-      <c r="AQ7">
-        <v>1.52</v>
-      </c>
-      <c r="AR7">
-        <v>1.83</v>
-      </c>
-      <c r="AS7">
-        <v>2.28</v>
-      </c>
-      <c r="AT7">
-        <v>2.95</v>
-      </c>
-      <c r="AU7">
-        <v>3.05</v>
-      </c>
-      <c r="AV7">
-        <v>2.3</v>
-      </c>
-      <c r="AW7">
-        <v>1.83</v>
-      </c>
-      <c r="AX7">
-        <v>1.52</v>
-      </c>
-      <c r="AY7">
-        <v>1.33</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>1.47</v>
-      </c>
-      <c r="BC7">
-        <v>3.1</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>251</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45754.47916666666</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45754</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F8" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2493,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L8">
         <v>2.25</v>
@@ -2568,93 +2136,39 @@
         <v>1.03</v>
       </c>
       <c r="AJ8" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="AK8" t="s">
-        <v>270</v>
-      </c>
-      <c r="AL8">
-        <v>1.25</v>
-      </c>
-      <c r="AM8">
-        <v>1.36</v>
-      </c>
-      <c r="AN8">
-        <v>1.75</v>
-      </c>
-      <c r="AO8">
-        <v>6</v>
-      </c>
-      <c r="AP8">
-        <v>1.53</v>
-      </c>
-      <c r="AQ8">
-        <v>1.82</v>
-      </c>
-      <c r="AR8">
-        <v>2.7</v>
-      </c>
-      <c r="AS8">
-        <v>3.9</v>
-      </c>
-      <c r="AT8">
-        <v>4.5</v>
-      </c>
-      <c r="AU8">
-        <v>2.25</v>
-      </c>
-      <c r="AV8">
-        <v>1.98</v>
-      </c>
-      <c r="AW8">
-        <v>1.38</v>
-      </c>
-      <c r="AX8">
-        <v>1.2</v>
-      </c>
-      <c r="AY8">
-        <v>1.13</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>1.62</v>
-      </c>
-      <c r="BC8">
-        <v>2.88</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>252</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45754.5</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45754</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="F9" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -2663,168 +2177,114 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L9">
-        <v>2.26</v>
+        <v>2.01</v>
       </c>
       <c r="M9">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="N9">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="O9">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="P9">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q9">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="R9">
         <v>1.4</v>
       </c>
       <c r="S9">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="T9">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U9">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V9">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z9">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AA9">
-        <v>2.4</v>
+        <v>3.42</v>
       </c>
       <c r="AB9">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="AC9">
+        <v>1.82</v>
+      </c>
+      <c r="AD9">
+        <v>2.92</v>
+      </c>
+      <c r="AE9">
+        <v>1.31</v>
+      </c>
+      <c r="AF9">
         <v>1.73</v>
       </c>
-      <c r="AD9">
-        <v>3.6</v>
-      </c>
-      <c r="AE9">
-        <v>1.21</v>
-      </c>
-      <c r="AF9">
-        <v>1.81</v>
-      </c>
       <c r="AG9">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AH9">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="AI9">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AJ9" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="AK9" t="s">
-        <v>270</v>
-      </c>
-      <c r="AL9">
-        <v>1.35</v>
-      </c>
-      <c r="AM9">
-        <v>1.31</v>
-      </c>
-      <c r="AN9">
-        <v>1.61</v>
-      </c>
-      <c r="AO9">
-        <v>9</v>
-      </c>
-      <c r="AP9">
-        <v>1.38</v>
-      </c>
-      <c r="AQ9">
-        <v>1.67</v>
-      </c>
-      <c r="AR9">
-        <v>2.1</v>
-      </c>
-      <c r="AS9">
-        <v>2.75</v>
-      </c>
-      <c r="AT9">
-        <v>3.8</v>
-      </c>
-      <c r="AU9">
-        <v>2.85</v>
-      </c>
-      <c r="AV9">
-        <v>2.1</v>
-      </c>
-      <c r="AW9">
-        <v>1.67</v>
-      </c>
-      <c r="AX9">
-        <v>1.4</v>
-      </c>
-      <c r="AY9">
-        <v>1.25</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>1.82</v>
-      </c>
-      <c r="BC9">
-        <v>2.18</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>208</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45754.5</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45754</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="F10" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -2833,195 +2293,141 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L10">
-        <v>2.01</v>
+        <v>2.26</v>
       </c>
       <c r="M10">
+        <v>3.45</v>
+      </c>
+      <c r="N10">
         <v>3.31</v>
       </c>
-      <c r="N10">
-        <v>3.32</v>
-      </c>
       <c r="O10">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="P10">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q10">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="R10">
         <v>1.4</v>
       </c>
       <c r="S10">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="T10">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U10">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="Z10">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="AA10">
-        <v>3.42</v>
+        <v>2.4</v>
       </c>
       <c r="AB10">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="AC10">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AD10">
-        <v>2.92</v>
+        <v>3.6</v>
       </c>
       <c r="AE10">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AF10">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AH10">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="AI10">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AJ10" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="AK10" t="s">
-        <v>226</v>
-      </c>
-      <c r="AL10">
-        <v>1.22</v>
-      </c>
-      <c r="AM10">
-        <v>1.25</v>
-      </c>
-      <c r="AN10">
-        <v>1.75</v>
-      </c>
-      <c r="AO10">
-        <v>9</v>
-      </c>
-      <c r="AP10">
-        <v>0</v>
-      </c>
-      <c r="AQ10">
-        <v>1.25</v>
-      </c>
-      <c r="AR10">
-        <v>1.45</v>
-      </c>
-      <c r="AS10">
-        <v>1.79</v>
-      </c>
-      <c r="AT10">
-        <v>2.24</v>
-      </c>
-      <c r="AU10">
-        <v>0</v>
-      </c>
-      <c r="AV10">
-        <v>3.28</v>
-      </c>
-      <c r="AW10">
-        <v>2.41</v>
-      </c>
-      <c r="AX10">
-        <v>1.87</v>
-      </c>
-      <c r="AY10">
-        <v>1.52</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>1.67</v>
-      </c>
-      <c r="BC10">
-        <v>2.5</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>252</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45754.5</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45754</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="F11" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L11">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="M11">
-        <v>3.29</v>
+        <v>3.6</v>
       </c>
       <c r="N11">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="P11">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="Q11">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="R11">
         <v>1.44</v>
@@ -3045,153 +2451,99 @@
         <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="Z11">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AA11">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="AB11">
         <v>1.85</v>
       </c>
       <c r="AC11">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AD11">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AE11">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF11">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AG11">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AH11">
-        <v>6.2</v>
+        <v>6.75</v>
       </c>
       <c r="AI11">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AJ11" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="AK11" t="s">
-        <v>271</v>
-      </c>
-      <c r="AL11">
-        <v>1.26</v>
-      </c>
-      <c r="AM11">
-        <v>1.29</v>
-      </c>
-      <c r="AN11">
-        <v>1.67</v>
-      </c>
-      <c r="AO11">
-        <v>-1</v>
-      </c>
-      <c r="AP11">
-        <v>1.36</v>
-      </c>
-      <c r="AQ11">
-        <v>1.68</v>
-      </c>
-      <c r="AR11">
-        <v>2.14</v>
-      </c>
-      <c r="AS11">
-        <v>2.88</v>
-      </c>
-      <c r="AT11">
-        <v>3.85</v>
-      </c>
-      <c r="AU11">
-        <v>2.7</v>
-      </c>
-      <c r="AV11">
-        <v>2.01</v>
-      </c>
-      <c r="AW11">
-        <v>1.57</v>
-      </c>
-      <c r="AX11">
-        <v>1.32</v>
-      </c>
-      <c r="AY11">
-        <v>1.2</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>1.83</v>
-      </c>
-      <c r="BC11">
-        <v>2.2</v>
-      </c>
-      <c r="BD11" s="3">
+        <v>208</v>
+      </c>
+      <c r="AL11" s="3">
         <v>45754.54166666666</v>
       </c>
     </row>
-    <row r="12" spans="1:56">
+    <row r="12" spans="1:38">
       <c r="A12" s="2">
         <v>45754</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F12" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L12">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="M12">
-        <v>3.76</v>
+        <v>4.6</v>
       </c>
       <c r="N12">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P12">
-        <v>14.25</v>
+        <v>11</v>
       </c>
       <c r="Q12">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="R12">
         <v>1.33</v>
@@ -3200,135 +2552,81 @@
         <v>3.25</v>
       </c>
       <c r="T12">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U12">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z12">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA12">
-        <v>3.86</v>
+        <v>4.2</v>
       </c>
       <c r="AB12">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AC12">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AD12">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AE12">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AF12">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG12">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH12">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="AI12">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AJ12" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="AK12" t="s">
-        <v>226</v>
-      </c>
-      <c r="AL12">
-        <v>1.07</v>
-      </c>
-      <c r="AM12">
-        <v>1.16</v>
-      </c>
-      <c r="AN12">
-        <v>2.64</v>
-      </c>
-      <c r="AO12">
-        <v>-1</v>
-      </c>
-      <c r="AP12">
-        <v>1.36</v>
-      </c>
-      <c r="AQ12">
-        <v>1.67</v>
-      </c>
-      <c r="AR12">
-        <v>2.1</v>
-      </c>
-      <c r="AS12">
-        <v>2.83</v>
-      </c>
-      <c r="AT12">
-        <v>3.75</v>
-      </c>
-      <c r="AU12">
-        <v>2.7</v>
-      </c>
-      <c r="AV12">
-        <v>2.03</v>
-      </c>
-      <c r="AW12">
-        <v>1.59</v>
-      </c>
-      <c r="AX12">
-        <v>1.33</v>
-      </c>
-      <c r="AY12">
-        <v>1.21</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>1.3</v>
-      </c>
-      <c r="BC12">
-        <v>3.75</v>
-      </c>
-      <c r="BD12" s="3">
+        <v>208</v>
+      </c>
+      <c r="AL12" s="3">
         <v>45754.54166666666</v>
       </c>
     </row>
-    <row r="13" spans="1:56">
+    <row r="13" spans="1:38">
       <c r="A13" s="2">
         <v>45754</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="F13" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="G13">
         <v>3</v>
@@ -3343,7 +2641,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L13">
         <v>1.92</v>
@@ -3418,427 +2716,265 @@
         <v>1.08</v>
       </c>
       <c r="AJ13" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="AK13" t="s">
-        <v>272</v>
-      </c>
-      <c r="AL13">
-        <v>1.22</v>
-      </c>
-      <c r="AM13">
-        <v>1.26</v>
-      </c>
-      <c r="AN13">
-        <v>1.79</v>
-      </c>
-      <c r="AO13">
-        <v>6</v>
-      </c>
-      <c r="AP13">
-        <v>1.32</v>
-      </c>
-      <c r="AQ13">
-        <v>1.6</v>
-      </c>
-      <c r="AR13">
-        <v>2.05</v>
-      </c>
-      <c r="AS13">
-        <v>2.7</v>
-      </c>
-      <c r="AT13">
-        <v>3.8</v>
-      </c>
-      <c r="AU13">
-        <v>2.88</v>
-      </c>
-      <c r="AV13">
-        <v>2.08</v>
-      </c>
-      <c r="AW13">
-        <v>1.65</v>
-      </c>
-      <c r="AX13">
-        <v>1.36</v>
-      </c>
-      <c r="AY13">
-        <v>1.19</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>1.62</v>
-      </c>
-      <c r="BC13">
-        <v>2.6</v>
-      </c>
-      <c r="BD13" s="3">
+        <v>253</v>
+      </c>
+      <c r="AL13" s="3">
         <v>45754.54166666666</v>
       </c>
     </row>
-    <row r="14" spans="1:56">
+    <row r="14" spans="1:38">
       <c r="A14" s="2">
         <v>45754</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E14" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="F14" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L14">
-        <v>1.62</v>
+        <v>7.1</v>
       </c>
       <c r="M14">
-        <v>3.6</v>
+        <v>3.99</v>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>1.47</v>
       </c>
       <c r="O14">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AC14">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AD14">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="AK14" t="s">
-        <v>226</v>
-      </c>
-      <c r="AL14">
-        <v>1.11</v>
-      </c>
-      <c r="AM14">
-        <v>1.22</v>
-      </c>
-      <c r="AN14">
-        <v>2.2</v>
-      </c>
-      <c r="AO14">
-        <v>12</v>
-      </c>
-      <c r="AP14">
-        <v>0</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14">
-        <v>0</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14">
-        <v>0</v>
-      </c>
-      <c r="AV14">
-        <v>0</v>
-      </c>
-      <c r="AW14">
-        <v>0</v>
-      </c>
-      <c r="AX14">
-        <v>0</v>
-      </c>
-      <c r="AY14">
-        <v>0</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>1.4</v>
-      </c>
-      <c r="BC14">
-        <v>3.5</v>
-      </c>
-      <c r="BD14" s="3">
+        <v>254</v>
+      </c>
+      <c r="AL14" s="3">
         <v>45754.54166666666</v>
       </c>
     </row>
-    <row r="15" spans="1:56">
+    <row r="15" spans="1:38">
       <c r="A15" s="2">
         <v>45754</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E15" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="F15" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L15">
-        <v>7.1</v>
+        <v>1.91</v>
       </c>
       <c r="M15">
-        <v>3.99</v>
+        <v>3.6</v>
       </c>
       <c r="N15">
-        <v>1.47</v>
+        <v>3.5</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB15">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="AC15">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ15" t="s">
-        <v>234</v>
+        <v>208</v>
       </c>
       <c r="AK15" t="s">
-        <v>273</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>0</v>
-      </c>
-      <c r="AO15">
-        <v>-1</v>
-      </c>
-      <c r="AP15">
-        <v>0</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>0</v>
-      </c>
-      <c r="AS15">
-        <v>0</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
-      </c>
-      <c r="AU15">
-        <v>0</v>
-      </c>
-      <c r="AV15">
-        <v>0</v>
-      </c>
-      <c r="AW15">
-        <v>0</v>
-      </c>
-      <c r="AX15">
-        <v>0</v>
-      </c>
-      <c r="AY15">
-        <v>0</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>0</v>
-      </c>
-      <c r="BC15">
-        <v>0</v>
-      </c>
-      <c r="BD15" s="3">
+        <v>255</v>
+      </c>
+      <c r="AL15" s="3">
         <v>45754.54166666666</v>
       </c>
     </row>
-    <row r="16" spans="1:56">
+    <row r="16" spans="1:38">
       <c r="A16" s="2">
         <v>45754</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E16" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="F16" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3853,195 +2989,141 @@
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L16">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="M16">
-        <v>3.6</v>
+        <v>3.29</v>
       </c>
       <c r="N16">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="O16">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="P16">
-        <v>11</v>
+        <v>7.7</v>
       </c>
       <c r="Q16">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="R16">
+        <v>1.44</v>
+      </c>
+      <c r="S16">
+        <v>2.63</v>
+      </c>
+      <c r="T16">
+        <v>3.25</v>
+      </c>
+      <c r="U16">
         <v>1.33</v>
       </c>
-      <c r="S16">
-        <v>3.1</v>
-      </c>
-      <c r="T16">
-        <v>2.4</v>
-      </c>
-      <c r="U16">
-        <v>1.5</v>
-      </c>
       <c r="V16">
-        <v>5.6</v>
+        <v>7.5</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>11.5</v>
+        <v>7.7</v>
       </c>
       <c r="Z16">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AA16">
-        <v>4.2</v>
+        <v>3.04</v>
       </c>
       <c r="AB16">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AC16">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AD16">
-        <v>2.68</v>
+        <v>3.28</v>
       </c>
       <c r="AE16">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AF16">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG16">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AH16">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AI16">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AJ16" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="AK16" t="s">
-        <v>274</v>
-      </c>
-      <c r="AL16">
-        <v>1.18</v>
-      </c>
-      <c r="AM16">
-        <v>1.22</v>
-      </c>
-      <c r="AN16">
-        <v>1.95</v>
-      </c>
-      <c r="AO16">
-        <v>10</v>
-      </c>
-      <c r="AP16">
-        <v>0</v>
-      </c>
-      <c r="AQ16">
-        <v>1.82</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
-      <c r="AS16">
-        <v>0</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
-      </c>
-      <c r="AU16">
-        <v>0</v>
-      </c>
-      <c r="AV16">
-        <v>1.98</v>
-      </c>
-      <c r="AW16">
-        <v>0</v>
-      </c>
-      <c r="AX16">
-        <v>0</v>
-      </c>
-      <c r="AY16">
-        <v>0</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>1.62</v>
-      </c>
-      <c r="BC16">
-        <v>2.55</v>
-      </c>
-      <c r="BD16" s="3">
+        <v>256</v>
+      </c>
+      <c r="AL16" s="3">
         <v>45754.54166666666</v>
       </c>
     </row>
-    <row r="17" spans="1:56">
+    <row r="17" spans="1:38">
       <c r="A17" s="2">
         <v>45754</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E17" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="F17" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L17">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="M17">
-        <v>4.6</v>
+        <v>3.76</v>
       </c>
       <c r="N17">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="O17">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P17">
-        <v>11</v>
+        <v>14.25</v>
       </c>
       <c r="Q17">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="R17">
         <v>1.33</v>
@@ -4050,135 +3132,81 @@
         <v>3.25</v>
       </c>
       <c r="T17">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U17">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V17">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W17">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z17">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AA17">
-        <v>4.2</v>
+        <v>3.86</v>
       </c>
       <c r="AB17">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AC17">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AD17">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AE17">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AF17">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG17">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH17">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="AI17">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AJ17" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="AK17" t="s">
-        <v>226</v>
-      </c>
-      <c r="AL17">
-        <v>1.02</v>
-      </c>
-      <c r="AM17">
-        <v>1.14</v>
-      </c>
-      <c r="AN17">
-        <v>3.1</v>
-      </c>
-      <c r="AO17">
-        <v>16</v>
-      </c>
-      <c r="AP17">
-        <v>0</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17">
-        <v>0</v>
-      </c>
-      <c r="AV17">
-        <v>0</v>
-      </c>
-      <c r="AW17">
-        <v>0</v>
-      </c>
-      <c r="AX17">
-        <v>0</v>
-      </c>
-      <c r="AY17">
-        <v>0</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>1.33</v>
-      </c>
-      <c r="BC17">
-        <v>3.85</v>
-      </c>
-      <c r="BD17" s="3">
+        <v>208</v>
+      </c>
+      <c r="AL17" s="3">
         <v>45754.54166666666</v>
       </c>
     </row>
-    <row r="18" spans="1:56">
+    <row r="18" spans="1:38">
       <c r="A18" s="2">
         <v>45754</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" t="s">
         <v>112</v>
       </c>
-      <c r="E18" t="s">
-        <v>130</v>
-      </c>
       <c r="F18" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -4193,7 +3221,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L18">
         <v>1.62</v>
@@ -4268,427 +3296,265 @@
         <v>1.15</v>
       </c>
       <c r="AJ18" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="AK18" t="s">
-        <v>226</v>
-      </c>
-      <c r="AL18">
-        <v>1.17</v>
-      </c>
-      <c r="AM18">
-        <v>1.18</v>
-      </c>
-      <c r="AN18">
-        <v>2.1</v>
-      </c>
-      <c r="AO18">
-        <v>13</v>
-      </c>
-      <c r="AP18">
-        <v>1.21</v>
-      </c>
-      <c r="AQ18">
-        <v>1.4</v>
-      </c>
-      <c r="AR18">
-        <v>1.67</v>
-      </c>
-      <c r="AS18">
-        <v>1.88</v>
-      </c>
-      <c r="AT18">
-        <v>2.6</v>
-      </c>
-      <c r="AU18">
-        <v>3.9</v>
-      </c>
-      <c r="AV18">
-        <v>2.7</v>
-      </c>
-      <c r="AW18">
-        <v>2.07</v>
-      </c>
-      <c r="AX18">
-        <v>1.92</v>
-      </c>
-      <c r="AY18">
-        <v>1.43</v>
-      </c>
-      <c r="AZ18">
-        <v>0</v>
-      </c>
-      <c r="BA18">
-        <v>0</v>
-      </c>
-      <c r="BB18">
-        <v>1.44</v>
-      </c>
-      <c r="BC18">
-        <v>2.75</v>
-      </c>
-      <c r="BD18" s="3">
+        <v>208</v>
+      </c>
+      <c r="AL18" s="3">
         <v>45754.5625</v>
       </c>
     </row>
-    <row r="19" spans="1:56">
+    <row r="19" spans="1:38">
       <c r="A19" s="2">
         <v>45754</v>
       </c>
       <c r="B19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" t="s">
         <v>64</v>
       </c>
-      <c r="C19" t="s">
-        <v>90</v>
-      </c>
       <c r="D19" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E19" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="F19" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L19">
-        <v>2.34</v>
+        <v>5.6</v>
       </c>
       <c r="M19">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="N19">
-        <v>3.03</v>
+        <v>1.56</v>
       </c>
       <c r="O19">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="P19">
-        <v>8.5</v>
+        <v>10.75</v>
       </c>
       <c r="Q19">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="R19">
+        <v>1.36</v>
+      </c>
+      <c r="S19">
+        <v>3</v>
+      </c>
+      <c r="T19">
+        <v>2.75</v>
+      </c>
+      <c r="U19">
         <v>1.4</v>
       </c>
-      <c r="S19">
-        <v>2.75</v>
-      </c>
-      <c r="T19">
-        <v>3</v>
-      </c>
-      <c r="U19">
-        <v>1.36</v>
-      </c>
       <c r="V19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>9.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z19">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AA19">
-        <v>3.63</v>
+        <v>3.26</v>
       </c>
       <c r="AB19">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AC19">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AD19">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="AE19">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF19">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG19">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH19">
-        <v>6.41</v>
+        <v>6.3</v>
       </c>
       <c r="AI19">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AJ19" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="AK19" t="s">
-        <v>275</v>
-      </c>
-      <c r="AL19">
-        <v>1.36</v>
-      </c>
-      <c r="AM19">
-        <v>1.25</v>
-      </c>
-      <c r="AN19">
-        <v>1.57</v>
-      </c>
-      <c r="AO19">
-        <v>9</v>
-      </c>
-      <c r="AP19">
-        <v>1.29</v>
-      </c>
-      <c r="AQ19">
-        <v>1.5</v>
-      </c>
-      <c r="AR19">
-        <v>1.81</v>
-      </c>
-      <c r="AS19">
-        <v>2.25</v>
-      </c>
-      <c r="AT19">
-        <v>2.9</v>
-      </c>
-      <c r="AU19">
-        <v>3.2</v>
-      </c>
-      <c r="AV19">
-        <v>2.4</v>
-      </c>
-      <c r="AW19">
-        <v>1.88</v>
-      </c>
-      <c r="AX19">
-        <v>1.55</v>
-      </c>
-      <c r="AY19">
-        <v>1.34</v>
-      </c>
-      <c r="AZ19">
-        <v>0</v>
-      </c>
-      <c r="BA19">
-        <v>0</v>
-      </c>
-      <c r="BB19">
-        <v>1.73</v>
-      </c>
-      <c r="BC19">
-        <v>2.2</v>
-      </c>
-      <c r="BD19" s="3">
+        <v>257</v>
+      </c>
+      <c r="AL19" s="3">
         <v>45754.58333333334</v>
       </c>
     </row>
-    <row r="20" spans="1:56">
+    <row r="20" spans="1:38">
       <c r="A20" s="2">
         <v>45754</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E20" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="F20" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
         <v>1</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L20">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="M20">
-        <v>3.05</v>
+        <v>3.32</v>
       </c>
       <c r="N20">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="O20">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="P20">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q20">
+        <v>1.67</v>
+      </c>
+      <c r="R20">
+        <v>1.33</v>
+      </c>
+      <c r="S20">
+        <v>3.25</v>
+      </c>
+      <c r="T20">
+        <v>2.63</v>
+      </c>
+      <c r="U20">
+        <v>1.44</v>
+      </c>
+      <c r="V20">
+        <v>6.5</v>
+      </c>
+      <c r="W20">
+        <v>1.11</v>
+      </c>
+      <c r="X20">
+        <v>1.04</v>
+      </c>
+      <c r="Y20">
+        <v>10</v>
+      </c>
+      <c r="Z20">
+        <v>1.22</v>
+      </c>
+      <c r="AA20">
+        <v>4.2</v>
+      </c>
+      <c r="AB20">
+        <v>1.7</v>
+      </c>
+      <c r="AC20">
         <v>2.1</v>
       </c>
-      <c r="R20">
-        <v>1.43</v>
-      </c>
-      <c r="S20">
-        <v>2.7</v>
-      </c>
-      <c r="T20">
-        <v>3.21</v>
-      </c>
-      <c r="U20">
-        <v>1.32</v>
-      </c>
-      <c r="V20">
-        <v>7.6</v>
-      </c>
-      <c r="W20">
-        <v>1.03</v>
-      </c>
-      <c r="X20">
-        <v>1.05</v>
-      </c>
-      <c r="Y20">
-        <v>8</v>
-      </c>
-      <c r="Z20">
-        <v>1.33</v>
-      </c>
-      <c r="AA20">
-        <v>3</v>
-      </c>
-      <c r="AB20">
-        <v>2.05</v>
-      </c>
-      <c r="AC20">
-        <v>1.61</v>
-      </c>
       <c r="AD20">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="AE20">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="AF20">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG20">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AH20">
-        <v>8</v>
+        <v>4.75</v>
       </c>
       <c r="AI20">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AJ20" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="AK20" t="s">
-        <v>276</v>
-      </c>
-      <c r="AL20">
-        <v>1.42</v>
-      </c>
-      <c r="AM20">
-        <v>1.35</v>
-      </c>
-      <c r="AN20">
-        <v>1.48</v>
-      </c>
-      <c r="AO20">
-        <v>8</v>
-      </c>
-      <c r="AP20">
-        <v>1.31</v>
-      </c>
-      <c r="AQ20">
-        <v>1.64</v>
-      </c>
-      <c r="AR20">
-        <v>2.05</v>
-      </c>
-      <c r="AS20">
-        <v>2.67</v>
-      </c>
-      <c r="AT20">
-        <v>3.58</v>
-      </c>
-      <c r="AU20">
-        <v>2.92</v>
-      </c>
-      <c r="AV20">
-        <v>2.21</v>
-      </c>
-      <c r="AW20">
-        <v>1.7</v>
-      </c>
-      <c r="AX20">
-        <v>1.39</v>
-      </c>
-      <c r="AY20">
-        <v>1.21</v>
-      </c>
-      <c r="AZ20">
-        <v>0</v>
-      </c>
-      <c r="BA20">
-        <v>0</v>
-      </c>
-      <c r="BB20">
-        <v>2</v>
-      </c>
-      <c r="BC20">
-        <v>2.1</v>
-      </c>
-      <c r="BD20" s="3">
+        <v>258</v>
+      </c>
+      <c r="AL20" s="3">
         <v>45754.58333333334</v>
       </c>
     </row>
-    <row r="21" spans="1:56">
+    <row r="21" spans="1:38">
       <c r="A21" s="2">
         <v>45754</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="D21" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="F21" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -4703,7 +3569,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L21">
         <v>2.08</v>
@@ -4778,257 +3644,149 @@
         <v>1.06</v>
       </c>
       <c r="AJ21" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="AK21" t="s">
-        <v>228</v>
-      </c>
-      <c r="AL21">
-        <v>1.36</v>
-      </c>
-      <c r="AM21">
-        <v>1.3</v>
-      </c>
-      <c r="AN21">
-        <v>1.61</v>
-      </c>
-      <c r="AO21">
-        <v>-1</v>
-      </c>
-      <c r="AP21">
-        <v>1.24</v>
-      </c>
-      <c r="AQ21">
-        <v>1.43</v>
-      </c>
-      <c r="AR21">
-        <v>1.7</v>
-      </c>
-      <c r="AS21">
-        <v>2.08</v>
-      </c>
-      <c r="AT21">
-        <v>2.65</v>
-      </c>
-      <c r="AU21">
-        <v>3.55</v>
-      </c>
-      <c r="AV21">
-        <v>2.63</v>
-      </c>
-      <c r="AW21">
-        <v>2.02</v>
-      </c>
-      <c r="AX21">
-        <v>1.66</v>
-      </c>
-      <c r="AY21">
-        <v>1.42</v>
-      </c>
-      <c r="AZ21">
-        <v>0</v>
-      </c>
-      <c r="BA21">
-        <v>0</v>
-      </c>
-      <c r="BB21">
-        <v>1.83</v>
-      </c>
-      <c r="BC21">
-        <v>2.12</v>
-      </c>
-      <c r="BD21" s="3">
+        <v>209</v>
+      </c>
+      <c r="AL21" s="3">
         <v>45754.58333333334</v>
       </c>
     </row>
-    <row r="22" spans="1:56">
+    <row r="22" spans="1:38">
       <c r="A22" s="2">
         <v>45754</v>
       </c>
       <c r="B22" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="E22" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="F22" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22" t="s">
+        <v>206</v>
+      </c>
+      <c r="L22">
+        <v>2.7</v>
+      </c>
+      <c r="M22">
+        <v>3.05</v>
+      </c>
+      <c r="N22">
+        <v>2.7</v>
+      </c>
+      <c r="O22">
         <v>2</v>
       </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>1</v>
-      </c>
-      <c r="K22" t="s">
-        <v>224</v>
-      </c>
-      <c r="L22">
-        <v>1.68</v>
-      </c>
-      <c r="M22">
+      <c r="P22">
+        <v>8</v>
+      </c>
+      <c r="Q22">
+        <v>2.1</v>
+      </c>
+      <c r="R22">
+        <v>1.43</v>
+      </c>
+      <c r="S22">
+        <v>2.7</v>
+      </c>
+      <c r="T22">
+        <v>3.21</v>
+      </c>
+      <c r="U22">
+        <v>1.32</v>
+      </c>
+      <c r="V22">
+        <v>7.6</v>
+      </c>
+      <c r="W22">
+        <v>1.03</v>
+      </c>
+      <c r="X22">
+        <v>1.05</v>
+      </c>
+      <c r="Y22">
+        <v>8</v>
+      </c>
+      <c r="Z22">
+        <v>1.33</v>
+      </c>
+      <c r="AA22">
+        <v>3</v>
+      </c>
+      <c r="AB22">
+        <v>2.05</v>
+      </c>
+      <c r="AC22">
+        <v>1.61</v>
+      </c>
+      <c r="AD22">
         <v>4</v>
       </c>
-      <c r="N22">
-        <v>4.4</v>
-      </c>
-      <c r="O22">
-        <v>1.7</v>
-      </c>
-      <c r="P22">
-        <v>12.75</v>
-      </c>
-      <c r="Q22">
-        <v>2.29</v>
-      </c>
-      <c r="R22">
-        <v>1.34</v>
-      </c>
-      <c r="S22">
-        <v>3.05</v>
-      </c>
-      <c r="T22">
-        <v>2.55</v>
-      </c>
-      <c r="U22">
-        <v>1.44</v>
-      </c>
-      <c r="V22">
-        <v>6.1</v>
-      </c>
-      <c r="W22">
-        <v>1.08</v>
-      </c>
-      <c r="X22">
-        <v>1.02</v>
-      </c>
-      <c r="Y22">
-        <v>10</v>
-      </c>
-      <c r="Z22">
-        <v>1.22</v>
-      </c>
-      <c r="AA22">
-        <v>3.52</v>
-      </c>
-      <c r="AB22">
-        <v>1.77</v>
-      </c>
-      <c r="AC22">
-        <v>1.98</v>
-      </c>
-      <c r="AD22">
-        <v>2.98</v>
-      </c>
       <c r="AE22">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AF22">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG22">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AH22">
-        <v>5.65</v>
+        <v>8</v>
       </c>
       <c r="AI22">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AJ22" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="AK22" t="s">
-        <v>277</v>
-      </c>
-      <c r="AL22">
-        <v>1.3</v>
-      </c>
-      <c r="AM22">
-        <v>1.26</v>
-      </c>
-      <c r="AN22">
-        <v>1.79</v>
-      </c>
-      <c r="AO22">
-        <v>-1</v>
-      </c>
-      <c r="AP22">
-        <v>1.18</v>
-      </c>
-      <c r="AQ22">
-        <v>1.32</v>
-      </c>
-      <c r="AR22">
-        <v>1.54</v>
-      </c>
-      <c r="AS22">
-        <v>1.84</v>
-      </c>
-      <c r="AT22">
-        <v>2.3</v>
-      </c>
-      <c r="AU22">
-        <v>4.1</v>
-      </c>
-      <c r="AV22">
-        <v>3.05</v>
-      </c>
-      <c r="AW22">
-        <v>2.3</v>
-      </c>
-      <c r="AX22">
-        <v>1.84</v>
-      </c>
-      <c r="AY22">
-        <v>1.54</v>
-      </c>
-      <c r="AZ22">
-        <v>0</v>
-      </c>
-      <c r="BA22">
-        <v>0</v>
-      </c>
-      <c r="BB22">
-        <v>1.7</v>
-      </c>
-      <c r="BC22">
-        <v>2.29</v>
-      </c>
-      <c r="BD22" s="3">
+        <v>259</v>
+      </c>
+      <c r="AL22" s="3">
         <v>45754.58333333334</v>
       </c>
     </row>
-    <row r="23" spans="1:56">
+    <row r="23" spans="1:38">
       <c r="A23" s="2">
         <v>45754</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E23" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="F23" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -5043,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L23">
         <v>1.7</v>
@@ -5118,141 +3876,87 @@
         <v>1.13</v>
       </c>
       <c r="AJ23" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="AK23" t="s">
-        <v>278</v>
-      </c>
-      <c r="AL23">
-        <v>1.18</v>
-      </c>
-      <c r="AM23">
-        <v>1.25</v>
-      </c>
-      <c r="AN23">
-        <v>2.1</v>
-      </c>
-      <c r="AO23">
-        <v>8</v>
-      </c>
-      <c r="AP23">
-        <v>1.2</v>
-      </c>
-      <c r="AQ23">
-        <v>1.36</v>
-      </c>
-      <c r="AR23">
-        <v>1.58</v>
-      </c>
-      <c r="AS23">
-        <v>1.92</v>
-      </c>
-      <c r="AT23">
-        <v>2.4</v>
-      </c>
-      <c r="AU23">
-        <v>3.95</v>
-      </c>
-      <c r="AV23">
-        <v>2.8</v>
-      </c>
-      <c r="AW23">
-        <v>2.18</v>
-      </c>
-      <c r="AX23">
-        <v>1.77</v>
-      </c>
-      <c r="AY23">
-        <v>1.5</v>
-      </c>
-      <c r="AZ23">
-        <v>0</v>
-      </c>
-      <c r="BA23">
-        <v>0</v>
-      </c>
-      <c r="BB23">
-        <v>1.44</v>
-      </c>
-      <c r="BC23">
-        <v>2.88</v>
-      </c>
-      <c r="BD23" s="3">
+        <v>260</v>
+      </c>
+      <c r="AL23" s="3">
         <v>45754.58333333334</v>
       </c>
     </row>
-    <row r="24" spans="1:56">
+    <row r="24" spans="1:38">
       <c r="A24" s="2">
         <v>45754</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="D24" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="E24" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="F24" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L24">
-        <v>3.15</v>
+        <v>1.68</v>
       </c>
       <c r="M24">
-        <v>3.32</v>
+        <v>4</v>
       </c>
       <c r="N24">
-        <v>2.18</v>
+        <v>4.4</v>
       </c>
       <c r="O24">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="P24">
-        <v>11</v>
+        <v>12.75</v>
       </c>
       <c r="Q24">
-        <v>1.67</v>
+        <v>2.29</v>
       </c>
       <c r="R24">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S24">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="T24">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="U24">
         <v>1.44</v>
       </c>
       <c r="V24">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="W24">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -5261,147 +3965,93 @@
         <v>1.22</v>
       </c>
       <c r="AA24">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="AB24">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC24">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AD24">
-        <v>2.65</v>
+        <v>2.98</v>
       </c>
       <c r="AE24">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AF24">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG24">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AH24">
-        <v>4.75</v>
+        <v>5.65</v>
       </c>
       <c r="AI24">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AJ24" t="s">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="AK24" t="s">
-        <v>279</v>
-      </c>
-      <c r="AL24">
-        <v>1.66</v>
-      </c>
-      <c r="AM24">
-        <v>1.28</v>
-      </c>
-      <c r="AN24">
-        <v>1.35</v>
-      </c>
-      <c r="AO24">
-        <v>9</v>
-      </c>
-      <c r="AP24">
-        <v>1.26</v>
-      </c>
-      <c r="AQ24">
-        <v>1.46</v>
-      </c>
-      <c r="AR24">
-        <v>1.74</v>
-      </c>
-      <c r="AS24">
-        <v>2.15</v>
-      </c>
-      <c r="AT24">
-        <v>2.7</v>
-      </c>
-      <c r="AU24">
-        <v>3.4</v>
-      </c>
-      <c r="AV24">
-        <v>2.5</v>
-      </c>
-      <c r="AW24">
-        <v>1.96</v>
-      </c>
-      <c r="AX24">
-        <v>1.61</v>
-      </c>
-      <c r="AY24">
-        <v>1.38</v>
-      </c>
-      <c r="AZ24">
-        <v>0</v>
-      </c>
-      <c r="BA24">
-        <v>0</v>
-      </c>
-      <c r="BB24">
-        <v>2.25</v>
-      </c>
-      <c r="BC24">
-        <v>1.67</v>
-      </c>
-      <c r="BD24" s="3">
+        <v>261</v>
+      </c>
+      <c r="AL24" s="3">
         <v>45754.58333333334</v>
       </c>
     </row>
-    <row r="25" spans="1:56">
+    <row r="25" spans="1:38">
       <c r="A25" s="2">
         <v>45754</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" t="s">
         <v>94</v>
       </c>
-      <c r="D25" t="s">
-        <v>112</v>
-      </c>
       <c r="E25" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="F25" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L25">
-        <v>5.5</v>
+        <v>2.34</v>
       </c>
       <c r="M25">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="N25">
-        <v>1.59</v>
+        <v>3.03</v>
       </c>
       <c r="O25">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="P25">
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="Q25">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="R25">
         <v>1.4</v>
@@ -5422,129 +4072,75 @@
         <v>1.08</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Z25">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AA25">
-        <v>3.25</v>
+        <v>3.63</v>
       </c>
       <c r="AB25">
         <v>1.95</v>
       </c>
       <c r="AC25">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AD25">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AE25">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF25">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AG25">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH25">
-        <v>6.5</v>
+        <v>6.41</v>
       </c>
       <c r="AI25">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AJ25" t="s">
-        <v>238</v>
+        <v>222</v>
       </c>
       <c r="AK25" t="s">
-        <v>251</v>
-      </c>
-      <c r="AL25">
-        <v>2.1</v>
-      </c>
-      <c r="AM25">
-        <v>1.26</v>
-      </c>
-      <c r="AN25">
-        <v>1.17</v>
-      </c>
-      <c r="AO25">
-        <v>9</v>
-      </c>
-      <c r="AP25">
-        <v>1.21</v>
-      </c>
-      <c r="AQ25">
-        <v>1.42</v>
-      </c>
-      <c r="AR25">
-        <v>1.75</v>
-      </c>
-      <c r="AS25">
-        <v>2.18</v>
-      </c>
-      <c r="AT25">
-        <v>2.92</v>
-      </c>
-      <c r="AU25">
-        <v>3.58</v>
-      </c>
-      <c r="AV25">
-        <v>2.57</v>
-      </c>
-      <c r="AW25">
-        <v>2.04</v>
-      </c>
-      <c r="AX25">
-        <v>1.65</v>
-      </c>
-      <c r="AY25">
-        <v>1.31</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>0</v>
-      </c>
-      <c r="BB25">
-        <v>3.1</v>
-      </c>
-      <c r="BC25">
-        <v>1.44</v>
-      </c>
-      <c r="BD25" s="3">
+        <v>262</v>
+      </c>
+      <c r="AL25" s="3">
         <v>45754.58333333334</v>
       </c>
     </row>
-    <row r="26" spans="1:56">
+    <row r="26" spans="1:38">
       <c r="A26" s="2">
         <v>45754</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D26" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E26" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="F26" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -5553,162 +4149,108 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L26">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="M26">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="N26">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="O26">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P26">
-        <v>10.75</v>
+        <v>8.75</v>
       </c>
       <c r="Q26">
         <v>1.44</v>
       </c>
       <c r="R26">
+        <v>1.4</v>
+      </c>
+      <c r="S26">
+        <v>2.75</v>
+      </c>
+      <c r="T26">
+        <v>3</v>
+      </c>
+      <c r="U26">
         <v>1.36</v>
       </c>
-      <c r="S26">
-        <v>3</v>
-      </c>
-      <c r="T26">
-        <v>2.75</v>
-      </c>
-      <c r="U26">
-        <v>1.4</v>
-      </c>
       <c r="V26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
         <v>9</v>
       </c>
       <c r="Z26">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AA26">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="AB26">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AC26">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AD26">
-        <v>3.31</v>
+        <v>3.5</v>
       </c>
       <c r="AE26">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF26">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AG26">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH26">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="AI26">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AJ26" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="AK26" t="s">
-        <v>280</v>
-      </c>
-      <c r="AL26">
-        <v>2.27</v>
-      </c>
-      <c r="AM26">
-        <v>1.26</v>
-      </c>
-      <c r="AN26">
-        <v>1.15</v>
-      </c>
-      <c r="AO26">
-        <v>5</v>
-      </c>
-      <c r="AP26">
-        <v>1.53</v>
-      </c>
-      <c r="AQ26">
-        <v>1.91</v>
-      </c>
-      <c r="AR26">
-        <v>2.43</v>
-      </c>
-      <c r="AS26">
-        <v>3.2</v>
-      </c>
-      <c r="AT26">
-        <v>4.35</v>
-      </c>
-      <c r="AU26">
-        <v>2.3</v>
-      </c>
-      <c r="AV26">
-        <v>1.78</v>
-      </c>
-      <c r="AW26">
-        <v>1.48</v>
-      </c>
-      <c r="AX26">
-        <v>1.29</v>
-      </c>
-      <c r="AY26">
-        <v>1.17</v>
-      </c>
-      <c r="AZ26">
-        <v>0</v>
-      </c>
-      <c r="BA26">
-        <v>0</v>
-      </c>
-      <c r="BB26">
-        <v>3</v>
-      </c>
-      <c r="BC26">
-        <v>1.44</v>
-      </c>
-      <c r="BD26" s="3">
+        <v>231</v>
+      </c>
+      <c r="AL26" s="3">
         <v>45754.58333333334</v>
       </c>
     </row>
-    <row r="27" spans="1:56">
+    <row r="27" spans="1:38">
       <c r="A27" s="2">
         <v>45754</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" t="s">
         <v>95</v>
       </c>
-      <c r="D27" t="s">
-        <v>113</v>
-      </c>
       <c r="E27" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="F27" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -5723,7 +4265,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L27">
         <v>1.63</v>
@@ -5798,87 +4340,33 @@
         <v>1.13</v>
       </c>
       <c r="AJ27" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="AK27" t="s">
-        <v>269</v>
-      </c>
-      <c r="AL27">
-        <v>1.18</v>
-      </c>
-      <c r="AM27">
-        <v>1.22</v>
-      </c>
-      <c r="AN27">
-        <v>2.05</v>
-      </c>
-      <c r="AO27">
-        <v>8</v>
-      </c>
-      <c r="AP27">
-        <v>1.19</v>
-      </c>
-      <c r="AQ27">
-        <v>1.33</v>
-      </c>
-      <c r="AR27">
-        <v>1.54</v>
-      </c>
-      <c r="AS27">
-        <v>1.85</v>
-      </c>
-      <c r="AT27">
-        <v>2.3</v>
-      </c>
-      <c r="AU27">
-        <v>4.1</v>
-      </c>
-      <c r="AV27">
-        <v>2.95</v>
-      </c>
-      <c r="AW27">
-        <v>2.3</v>
-      </c>
-      <c r="AX27">
-        <v>1.83</v>
-      </c>
-      <c r="AY27">
-        <v>1.54</v>
-      </c>
-      <c r="AZ27">
-        <v>0</v>
-      </c>
-      <c r="BA27">
-        <v>0</v>
-      </c>
-      <c r="BB27">
-        <v>1.44</v>
-      </c>
-      <c r="BC27">
-        <v>2.88</v>
-      </c>
-      <c r="BD27" s="3">
+        <v>250</v>
+      </c>
+      <c r="AL27" s="3">
         <v>45754.59027777778</v>
       </c>
     </row>
-    <row r="28" spans="1:56">
+    <row r="28" spans="1:38">
       <c r="A28" s="2">
         <v>45754</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E28" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="F28" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -5893,7 +4381,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L28">
         <v>2.34</v>
@@ -5968,87 +4456,33 @@
         <v>1.05</v>
       </c>
       <c r="AJ28" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="AK28" t="s">
-        <v>226</v>
-      </c>
-      <c r="AL28">
-        <v>1.25</v>
-      </c>
-      <c r="AM28">
-        <v>1.35</v>
-      </c>
-      <c r="AN28">
-        <v>1.78</v>
-      </c>
-      <c r="AO28">
-        <v>-1</v>
-      </c>
-      <c r="AP28">
-        <v>1.3</v>
-      </c>
-      <c r="AQ28">
-        <v>1.53</v>
-      </c>
-      <c r="AR28">
-        <v>1.88</v>
-      </c>
-      <c r="AS28">
-        <v>2.35</v>
-      </c>
-      <c r="AT28">
-        <v>3.05</v>
-      </c>
-      <c r="AU28">
-        <v>3.05</v>
-      </c>
-      <c r="AV28">
-        <v>2.28</v>
-      </c>
-      <c r="AW28">
-        <v>1.78</v>
-      </c>
-      <c r="AX28">
-        <v>1.49</v>
-      </c>
-      <c r="AY28">
-        <v>1.3</v>
-      </c>
-      <c r="AZ28">
-        <v>0</v>
-      </c>
-      <c r="BA28">
-        <v>0</v>
-      </c>
-      <c r="BB28">
-        <v>1.8</v>
-      </c>
-      <c r="BC28">
-        <v>2.5</v>
-      </c>
-      <c r="BD28" s="3">
+        <v>208</v>
+      </c>
+      <c r="AL28" s="3">
         <v>45754.60416666666</v>
       </c>
     </row>
-    <row r="29" spans="1:56">
+    <row r="29" spans="1:38">
       <c r="A29" s="2">
         <v>45754</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D29" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E29" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="F29" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6063,7 +4497,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L29">
         <v>2.69</v>
@@ -6138,87 +4572,33 @@
         <v>1.16</v>
       </c>
       <c r="AJ29" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="AK29" t="s">
-        <v>281</v>
-      </c>
-      <c r="AL29">
-        <v>1.53</v>
-      </c>
-      <c r="AM29">
-        <v>1.27</v>
-      </c>
-      <c r="AN29">
-        <v>1.47</v>
-      </c>
-      <c r="AO29">
-        <v>8</v>
-      </c>
-      <c r="AP29">
-        <v>1.32</v>
-      </c>
-      <c r="AQ29">
-        <v>1.7</v>
-      </c>
-      <c r="AR29">
-        <v>2.06</v>
-      </c>
-      <c r="AS29">
-        <v>2.71</v>
-      </c>
-      <c r="AT29">
-        <v>3.74</v>
-      </c>
-      <c r="AU29">
-        <v>2.88</v>
-      </c>
-      <c r="AV29">
-        <v>2.05</v>
-      </c>
-      <c r="AW29">
-        <v>1.68</v>
-      </c>
-      <c r="AX29">
-        <v>1.38</v>
-      </c>
-      <c r="AY29">
-        <v>1.19</v>
-      </c>
-      <c r="AZ29">
-        <v>0</v>
-      </c>
-      <c r="BA29">
-        <v>0</v>
-      </c>
-      <c r="BB29">
-        <v>1.97</v>
-      </c>
-      <c r="BC29">
-        <v>1.87</v>
-      </c>
-      <c r="BD29" s="3">
+        <v>263</v>
+      </c>
+      <c r="AL29" s="3">
         <v>45754.60416666666</v>
       </c>
     </row>
-    <row r="30" spans="1:56">
+    <row r="30" spans="1:38">
       <c r="A30" s="2">
         <v>45754</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D30" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E30" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="F30" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6233,7 +4613,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L30">
         <v>2.8</v>
@@ -6308,597 +4688,381 @@
         <v>1.01</v>
       </c>
       <c r="AJ30" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="AK30" t="s">
-        <v>226</v>
-      </c>
-      <c r="AL30">
-        <v>1.46</v>
-      </c>
-      <c r="AM30">
-        <v>1.35</v>
-      </c>
-      <c r="AN30">
-        <v>1.44</v>
-      </c>
-      <c r="AO30">
-        <v>16</v>
-      </c>
-      <c r="AP30">
-        <v>1.21</v>
-      </c>
-      <c r="AQ30">
-        <v>1.43</v>
-      </c>
-      <c r="AR30">
-        <v>1.77</v>
-      </c>
-      <c r="AS30">
-        <v>2.23</v>
-      </c>
-      <c r="AT30">
-        <v>2.97</v>
-      </c>
-      <c r="AU30">
-        <v>3.58</v>
-      </c>
-      <c r="AV30">
-        <v>2.54</v>
-      </c>
-      <c r="AW30">
-        <v>1.94</v>
-      </c>
-      <c r="AX30">
-        <v>1.55</v>
-      </c>
-      <c r="AY30">
-        <v>1.3</v>
-      </c>
-      <c r="AZ30">
-        <v>0</v>
-      </c>
-      <c r="BA30">
-        <v>0</v>
-      </c>
-      <c r="BB30">
-        <v>1.91</v>
-      </c>
-      <c r="BC30">
-        <v>2.25</v>
-      </c>
-      <c r="BD30" s="3">
+        <v>208</v>
+      </c>
+      <c r="AL30" s="3">
         <v>45754.61458333334</v>
       </c>
     </row>
-    <row r="31" spans="1:56">
+    <row r="31" spans="1:38">
       <c r="A31" s="2">
         <v>45754</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D31" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E31" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="F31" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="G31">
+        <v>3</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
         <v>2</v>
       </c>
-      <c r="H31">
-        <v>2</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
       <c r="J31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L31">
-        <v>1.55</v>
+        <v>4.5</v>
       </c>
       <c r="M31">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="N31">
-        <v>4.75</v>
+        <v>1.65</v>
       </c>
       <c r="O31">
-        <v>1.4</v>
+        <v>2.63</v>
       </c>
       <c r="P31">
-        <v>21</v>
+        <v>9.1</v>
       </c>
       <c r="Q31">
-        <v>2.75</v>
+        <v>1.62</v>
       </c>
       <c r="R31">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="S31">
-        <v>4</v>
+        <v>2.61</v>
       </c>
       <c r="T31">
-        <v>2</v>
+        <v>2.94</v>
       </c>
       <c r="U31">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="V31">
-        <v>4.33</v>
+        <v>7</v>
       </c>
       <c r="W31">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y31">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Z31">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AA31">
-        <v>6.5</v>
+        <v>2.9</v>
       </c>
       <c r="AB31">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="AC31">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="AD31">
-        <v>1.87</v>
+        <v>3.6</v>
       </c>
       <c r="AE31">
+        <v>1.25</v>
+      </c>
+      <c r="AF31">
+        <v>1.91</v>
+      </c>
+      <c r="AG31">
         <v>1.8</v>
       </c>
-      <c r="AF31">
-        <v>1.44</v>
-      </c>
-      <c r="AG31">
-        <v>2.63</v>
-      </c>
       <c r="AH31">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="AI31">
-        <v>1.36</v>
+        <v>1.07</v>
       </c>
       <c r="AJ31" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="AK31" t="s">
-        <v>282</v>
-      </c>
-      <c r="AL31">
-        <v>1.17</v>
-      </c>
-      <c r="AM31">
-        <v>1.15</v>
-      </c>
-      <c r="AN31">
-        <v>2.45</v>
-      </c>
-      <c r="AO31">
-        <v>-1</v>
-      </c>
-      <c r="AP31">
-        <v>1.22</v>
-      </c>
-      <c r="AQ31">
-        <v>1.4</v>
-      </c>
-      <c r="AR31">
-        <v>1.66</v>
-      </c>
-      <c r="AS31">
-        <v>2.02</v>
-      </c>
-      <c r="AT31">
-        <v>2.5</v>
-      </c>
-      <c r="AU31">
-        <v>3.7</v>
-      </c>
-      <c r="AV31">
-        <v>2.7</v>
-      </c>
-      <c r="AW31">
-        <v>2.08</v>
-      </c>
-      <c r="AX31">
-        <v>1.7</v>
-      </c>
-      <c r="AY31">
-        <v>1.46</v>
-      </c>
-      <c r="AZ31">
-        <v>0</v>
-      </c>
-      <c r="BA31">
-        <v>0</v>
-      </c>
-      <c r="BB31">
-        <v>1.4</v>
-      </c>
-      <c r="BC31">
-        <v>2.75</v>
-      </c>
-      <c r="BD31" s="3">
+        <v>208</v>
+      </c>
+      <c r="AL31" s="3">
         <v>45754.625</v>
       </c>
     </row>
-    <row r="32" spans="1:56">
+    <row r="32" spans="1:38">
       <c r="A32" s="2">
         <v>45754</v>
       </c>
       <c r="B32" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E32" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="F32" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L32">
+        <v>6</v>
+      </c>
+      <c r="M32">
         <v>4.5</v>
       </c>
-      <c r="M32">
-        <v>3.9</v>
-      </c>
       <c r="N32">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="O32">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>9.1</v>
+        <v>16.5</v>
       </c>
       <c r="Q32">
+        <v>1.33</v>
+      </c>
+      <c r="R32">
+        <v>1.3</v>
+      </c>
+      <c r="S32">
+        <v>3.4</v>
+      </c>
+      <c r="T32">
+        <v>2.5</v>
+      </c>
+      <c r="U32">
+        <v>1.5</v>
+      </c>
+      <c r="V32">
+        <v>6</v>
+      </c>
+      <c r="W32">
+        <v>1.13</v>
+      </c>
+      <c r="X32">
+        <v>1.02</v>
+      </c>
+      <c r="Y32">
+        <v>13.2</v>
+      </c>
+      <c r="Z32">
+        <v>1.15</v>
+      </c>
+      <c r="AA32">
+        <v>4.2</v>
+      </c>
+      <c r="AB32">
         <v>1.62</v>
       </c>
-      <c r="R32">
-        <v>1.41</v>
-      </c>
-      <c r="S32">
-        <v>2.61</v>
-      </c>
-      <c r="T32">
-        <v>2.94</v>
-      </c>
-      <c r="U32">
-        <v>1.33</v>
-      </c>
-      <c r="V32">
-        <v>7</v>
-      </c>
-      <c r="W32">
-        <v>1.07</v>
-      </c>
-      <c r="X32">
-        <v>1.05</v>
-      </c>
-      <c r="Y32">
-        <v>8</v>
-      </c>
-      <c r="Z32">
-        <v>1.36</v>
-      </c>
-      <c r="AA32">
-        <v>2.9</v>
-      </c>
-      <c r="AB32">
-        <v>2.15</v>
-      </c>
       <c r="AC32">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="AD32">
-        <v>3.6</v>
+        <v>2.43</v>
       </c>
       <c r="AE32">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF32">
+        <v>1.8</v>
+      </c>
+      <c r="AG32">
         <v>1.91</v>
       </c>
-      <c r="AG32">
-        <v>1.8</v>
-      </c>
       <c r="AH32">
-        <v>7</v>
+        <v>4.25</v>
       </c>
       <c r="AI32">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AJ32" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="AK32" t="s">
-        <v>226</v>
-      </c>
-      <c r="AL32">
-        <v>1.78</v>
-      </c>
-      <c r="AM32">
-        <v>1.33</v>
-      </c>
-      <c r="AN32">
-        <v>1.29</v>
-      </c>
-      <c r="AO32">
-        <v>12</v>
-      </c>
-      <c r="AP32">
-        <v>0</v>
-      </c>
-      <c r="AQ32">
-        <v>1.48</v>
-      </c>
-      <c r="AR32">
-        <v>1.88</v>
-      </c>
-      <c r="AS32">
-        <v>2.4</v>
-      </c>
-      <c r="AT32">
-        <v>3.3</v>
-      </c>
-      <c r="AU32">
-        <v>0</v>
-      </c>
-      <c r="AV32">
-        <v>2.5</v>
-      </c>
-      <c r="AW32">
-        <v>1.92</v>
-      </c>
-      <c r="AX32">
-        <v>1.52</v>
-      </c>
-      <c r="AY32">
-        <v>1.3</v>
-      </c>
-      <c r="AZ32">
-        <v>0</v>
-      </c>
-      <c r="BA32">
-        <v>0</v>
-      </c>
-      <c r="BB32">
-        <v>2.63</v>
-      </c>
-      <c r="BC32">
-        <v>1.62</v>
-      </c>
-      <c r="BD32" s="3">
+        <v>264</v>
+      </c>
+      <c r="AL32" s="3">
         <v>45754.625</v>
       </c>
     </row>
-    <row r="33" spans="1:56">
+    <row r="33" spans="1:38">
       <c r="A33" s="2">
         <v>45754</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D33" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E33" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="F33" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L33">
-        <v>6</v>
+        <v>1.55</v>
       </c>
       <c r="M33">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="N33">
-        <v>1.48</v>
+        <v>4.75</v>
       </c>
       <c r="O33">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="P33">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="Q33">
-        <v>1.33</v>
+        <v>2.75</v>
       </c>
       <c r="R33">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S33">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="T33">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="U33">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="V33">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="W33">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>13.2</v>
+        <v>17</v>
       </c>
       <c r="Z33">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AA33">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="AB33">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AC33">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD33">
-        <v>2.43</v>
+        <v>1.87</v>
       </c>
       <c r="AE33">
+        <v>1.8</v>
+      </c>
+      <c r="AF33">
         <v>1.44</v>
       </c>
-      <c r="AF33">
-        <v>1.8</v>
-      </c>
       <c r="AG33">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="AH33">
-        <v>4.25</v>
+        <v>3.1</v>
       </c>
       <c r="AI33">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AJ33" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="AK33" t="s">
-        <v>283</v>
-      </c>
-      <c r="AL33">
-        <v>2.58</v>
-      </c>
-      <c r="AM33">
-        <v>1.18</v>
-      </c>
-      <c r="AN33">
-        <v>1.12</v>
-      </c>
-      <c r="AO33">
-        <v>-1</v>
-      </c>
-      <c r="AP33">
-        <v>1.24</v>
-      </c>
-      <c r="AQ33">
-        <v>1.33</v>
-      </c>
-      <c r="AR33">
-        <v>1.69</v>
-      </c>
-      <c r="AS33">
-        <v>2.07</v>
-      </c>
-      <c r="AT33">
-        <v>2.6</v>
-      </c>
-      <c r="AU33">
-        <v>3.55</v>
-      </c>
-      <c r="AV33">
-        <v>2.83</v>
-      </c>
-      <c r="AW33">
-        <v>2.13</v>
-      </c>
-      <c r="AX33">
-        <v>1.73</v>
-      </c>
-      <c r="AY33">
-        <v>1.41</v>
-      </c>
-      <c r="AZ33">
-        <v>0</v>
-      </c>
-      <c r="BA33">
-        <v>0</v>
-      </c>
-      <c r="BB33">
-        <v>3.4</v>
-      </c>
-      <c r="BC33">
-        <v>1.33</v>
-      </c>
-      <c r="BD33" s="3">
+        <v>265</v>
+      </c>
+      <c r="AL33" s="3">
         <v>45754.625</v>
       </c>
     </row>
-    <row r="34" spans="1:56">
+    <row r="34" spans="1:38">
       <c r="A34" s="2">
         <v>45754</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="D34" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E34" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="F34" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -6913,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L34">
         <v>1.3</v>
@@ -6988,257 +5152,149 @@
         <v>1.36</v>
       </c>
       <c r="AJ34" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="AK34" t="s">
-        <v>226</v>
-      </c>
-      <c r="AL34">
-        <v>1.06</v>
-      </c>
-      <c r="AM34">
-        <v>1.12</v>
-      </c>
-      <c r="AN34">
-        <v>3.5</v>
-      </c>
-      <c r="AO34">
-        <v>7</v>
-      </c>
-      <c r="AP34">
-        <v>1.08</v>
-      </c>
-      <c r="AQ34">
-        <v>1.17</v>
-      </c>
-      <c r="AR34">
-        <v>1.31</v>
-      </c>
-      <c r="AS34">
-        <v>1.54</v>
-      </c>
-      <c r="AT34">
-        <v>1.87</v>
-      </c>
-      <c r="AU34">
-        <v>6.15</v>
-      </c>
-      <c r="AV34">
-        <v>4.2</v>
-      </c>
-      <c r="AW34">
-        <v>3.05</v>
-      </c>
-      <c r="AX34">
-        <v>2.31</v>
-      </c>
-      <c r="AY34">
-        <v>1.87</v>
-      </c>
-      <c r="AZ34">
-        <v>0</v>
-      </c>
-      <c r="BA34">
-        <v>0</v>
-      </c>
-      <c r="BB34">
-        <v>1.25</v>
-      </c>
-      <c r="BC34">
-        <v>3.75</v>
-      </c>
-      <c r="BD34" s="3">
+        <v>208</v>
+      </c>
+      <c r="AL34" s="3">
         <v>45754.625</v>
       </c>
     </row>
-    <row r="35" spans="1:56">
+    <row r="35" spans="1:38">
       <c r="A35" s="2">
         <v>45754</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D35" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="E35" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="F35" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L35">
-        <v>1.43</v>
+        <v>3</v>
       </c>
       <c r="M35">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="N35">
-        <v>7.8</v>
+        <v>2.8</v>
       </c>
       <c r="O35">
-        <v>1.29</v>
+        <v>2.4</v>
       </c>
       <c r="P35">
-        <v>8.699999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="Q35">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="R35">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="S35">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="T35">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="U35">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="V35">
-        <v>7.5</v>
+        <v>21</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="Y35">
-        <v>8.699999999999999</v>
+        <v>4.33</v>
       </c>
       <c r="Z35">
-        <v>1.3</v>
+        <v>1.84</v>
       </c>
       <c r="AA35">
-        <v>2.97</v>
+        <v>1.91</v>
       </c>
       <c r="AB35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC35">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AD35">
-        <v>3.7</v>
+        <v>8.5</v>
       </c>
       <c r="AE35">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AF35">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AG35">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AH35">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="AI35">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ35" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="AK35" t="s">
-        <v>284</v>
-      </c>
-      <c r="AL35">
-        <v>1.01</v>
-      </c>
-      <c r="AM35">
-        <v>1.18</v>
-      </c>
-      <c r="AN35">
-        <v>2.68</v>
-      </c>
-      <c r="AO35">
-        <v>9</v>
-      </c>
-      <c r="AP35">
-        <v>1.33</v>
-      </c>
-      <c r="AQ35">
-        <v>1.61</v>
-      </c>
-      <c r="AR35">
-        <v>2.05</v>
-      </c>
-      <c r="AS35">
-        <v>2.7</v>
-      </c>
-      <c r="AT35">
-        <v>3.78</v>
-      </c>
-      <c r="AU35">
-        <v>2.83</v>
-      </c>
-      <c r="AV35">
-        <v>2.07</v>
-      </c>
-      <c r="AW35">
-        <v>1.65</v>
-      </c>
-      <c r="AX35">
-        <v>1.36</v>
-      </c>
-      <c r="AY35">
-        <v>1.19</v>
-      </c>
-      <c r="AZ35">
-        <v>0</v>
-      </c>
-      <c r="BA35">
-        <v>0</v>
-      </c>
-      <c r="BB35">
-        <v>1.29</v>
-      </c>
-      <c r="BC35">
-        <v>4.5</v>
-      </c>
-      <c r="BD35" s="3">
+        <v>208</v>
+      </c>
+      <c r="AL35" s="3">
         <v>45754.64583333334</v>
       </c>
     </row>
-    <row r="36" spans="1:56">
+    <row r="36" spans="1:38">
       <c r="A36" s="2">
         <v>45754</v>
       </c>
       <c r="B36" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="D36" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="E36" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="F36" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -7247,201 +5303,147 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L36">
+        <v>1.33</v>
+      </c>
+      <c r="M36">
+        <v>5.1</v>
+      </c>
+      <c r="N36">
+        <v>11</v>
+      </c>
+      <c r="O36">
+        <v>1.22</v>
+      </c>
+      <c r="P36">
+        <v>8.5</v>
+      </c>
+      <c r="Q36">
+        <v>5</v>
+      </c>
+      <c r="R36">
+        <v>1.44</v>
+      </c>
+      <c r="S36">
+        <v>2.63</v>
+      </c>
+      <c r="T36">
+        <v>3.25</v>
+      </c>
+      <c r="U36">
+        <v>1.33</v>
+      </c>
+      <c r="V36">
+        <v>10</v>
+      </c>
+      <c r="W36">
+        <v>1.06</v>
+      </c>
+      <c r="X36">
+        <v>1.01</v>
+      </c>
+      <c r="Y36">
+        <v>8.5</v>
+      </c>
+      <c r="Z36">
+        <v>1.33</v>
+      </c>
+      <c r="AA36">
+        <v>2.9</v>
+      </c>
+      <c r="AB36">
+        <v>2.1</v>
+      </c>
+      <c r="AC36">
+        <v>1.61</v>
+      </c>
+      <c r="AD36">
+        <v>3.82</v>
+      </c>
+      <c r="AE36">
+        <v>1.2</v>
+      </c>
+      <c r="AF36">
         <v>3</v>
       </c>
-      <c r="M36">
-        <v>2.75</v>
-      </c>
-      <c r="N36">
-        <v>2.8</v>
-      </c>
-      <c r="O36">
-        <v>2.4</v>
-      </c>
-      <c r="P36">
-        <v>4.2</v>
-      </c>
-      <c r="Q36">
-        <v>2.1</v>
-      </c>
-      <c r="R36">
-        <v>1.83</v>
-      </c>
-      <c r="S36">
-        <v>1.83</v>
-      </c>
-      <c r="T36">
-        <v>6</v>
-      </c>
-      <c r="U36">
-        <v>1.13</v>
-      </c>
-      <c r="V36">
-        <v>21</v>
-      </c>
-      <c r="W36">
-        <v>1.02</v>
-      </c>
-      <c r="X36">
-        <v>1.2</v>
-      </c>
-      <c r="Y36">
-        <v>4.33</v>
-      </c>
-      <c r="Z36">
-        <v>1.84</v>
-      </c>
-      <c r="AA36">
-        <v>1.91</v>
-      </c>
-      <c r="AB36">
-        <v>4</v>
-      </c>
-      <c r="AC36">
-        <v>1.25</v>
-      </c>
-      <c r="AD36">
-        <v>8.5</v>
-      </c>
-      <c r="AE36">
-        <v>1.06</v>
-      </c>
-      <c r="AF36">
-        <v>2.75</v>
-      </c>
       <c r="AG36">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH36">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="AI36">
         <v>1.03</v>
       </c>
       <c r="AJ36" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="AK36" t="s">
-        <v>226</v>
-      </c>
-      <c r="AL36">
-        <v>1.38</v>
-      </c>
-      <c r="AM36">
-        <v>1.49</v>
-      </c>
-      <c r="AN36">
-        <v>1.38</v>
-      </c>
-      <c r="AO36">
-        <v>-1</v>
-      </c>
-      <c r="AP36">
-        <v>1.65</v>
-      </c>
-      <c r="AQ36">
-        <v>2.06</v>
-      </c>
-      <c r="AR36">
-        <v>2.65</v>
-      </c>
-      <c r="AS36">
-        <v>3.55</v>
-      </c>
-      <c r="AT36">
-        <v>4.8</v>
-      </c>
-      <c r="AU36">
-        <v>2.08</v>
-      </c>
-      <c r="AV36">
-        <v>1.66</v>
-      </c>
-      <c r="AW36">
-        <v>1.41</v>
-      </c>
-      <c r="AX36">
-        <v>1.24</v>
-      </c>
-      <c r="AY36">
-        <v>1.14</v>
-      </c>
-      <c r="AZ36">
-        <v>0</v>
-      </c>
-      <c r="BA36">
-        <v>0</v>
-      </c>
-      <c r="BB36">
-        <v>2.4</v>
-      </c>
-      <c r="BC36">
-        <v>2.1</v>
-      </c>
-      <c r="BD36" s="3">
+        <v>208</v>
+      </c>
+      <c r="AL36" s="3">
         <v>45754.64583333334</v>
       </c>
     </row>
-    <row r="37" spans="1:56">
+    <row r="37" spans="1:38">
       <c r="A37" s="2">
         <v>45754</v>
       </c>
       <c r="B37" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="D37" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E37" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="F37" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="G37">
         <v>1</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37">
         <v>1</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L37">
-        <v>1.33</v>
+        <v>2.7</v>
       </c>
       <c r="M37">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="N37">
-        <v>11</v>
+        <v>2.45</v>
       </c>
       <c r="O37">
-        <v>1.22</v>
+        <v>1.83</v>
       </c>
       <c r="P37">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q37">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="R37">
         <v>1.44</v>
@@ -7450,13 +5452,13 @@
         <v>2.63</v>
       </c>
       <c r="T37">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U37">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W37">
         <v>1.06</v>
@@ -7465,120 +5467,66 @@
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z37">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AA37">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AB37">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC37">
         <v>1.61</v>
       </c>
       <c r="AD37">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="AE37">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF37">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="AG37">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AH37">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AI37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ37" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="AK37" t="s">
-        <v>226</v>
-      </c>
-      <c r="AL37">
-        <v>1.06</v>
-      </c>
-      <c r="AM37">
-        <v>1.2</v>
-      </c>
-      <c r="AN37">
-        <v>3.25</v>
-      </c>
-      <c r="AO37">
-        <v>-1</v>
-      </c>
-      <c r="AP37">
-        <v>1.42</v>
-      </c>
-      <c r="AQ37">
-        <v>1.72</v>
-      </c>
-      <c r="AR37">
-        <v>2.15</v>
-      </c>
-      <c r="AS37">
-        <v>2.75</v>
-      </c>
-      <c r="AT37">
-        <v>3.65</v>
-      </c>
-      <c r="AU37">
-        <v>2.55</v>
-      </c>
-      <c r="AV37">
-        <v>1.95</v>
-      </c>
-      <c r="AW37">
-        <v>1.6</v>
-      </c>
-      <c r="AX37">
-        <v>1.37</v>
-      </c>
-      <c r="AY37">
-        <v>1.22</v>
-      </c>
-      <c r="AZ37">
-        <v>0</v>
-      </c>
-      <c r="BA37">
-        <v>0</v>
-      </c>
-      <c r="BB37">
-        <v>1.22</v>
-      </c>
-      <c r="BC37">
-        <v>5</v>
-      </c>
-      <c r="BD37" s="3">
+        <v>266</v>
+      </c>
+      <c r="AL37" s="3">
         <v>45754.64583333334</v>
       </c>
     </row>
-    <row r="38" spans="1:56">
+    <row r="38" spans="1:38">
       <c r="A38" s="2">
         <v>45754</v>
       </c>
       <c r="B38" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D38" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E38" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="F38" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="G38">
         <v>3</v>
@@ -7593,7 +5541,7 @@
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L38">
         <v>1.93</v>
@@ -7668,120 +5616,66 @@
         <v>1.01</v>
       </c>
       <c r="AJ38" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="AK38" t="s">
-        <v>285</v>
-      </c>
-      <c r="AL38">
-        <v>1.14</v>
-      </c>
-      <c r="AM38">
-        <v>1.28</v>
-      </c>
-      <c r="AN38">
-        <v>1.78</v>
-      </c>
-      <c r="AO38">
-        <v>7</v>
-      </c>
-      <c r="AP38">
-        <v>1.33</v>
-      </c>
-      <c r="AQ38">
-        <v>1.62</v>
-      </c>
-      <c r="AR38">
-        <v>2.09</v>
-      </c>
-      <c r="AS38">
-        <v>2.74</v>
-      </c>
-      <c r="AT38">
-        <v>3.85</v>
-      </c>
-      <c r="AU38">
-        <v>2.83</v>
-      </c>
-      <c r="AV38">
-        <v>2.06</v>
-      </c>
-      <c r="AW38">
-        <v>1.63</v>
-      </c>
-      <c r="AX38">
-        <v>1.35</v>
-      </c>
-      <c r="AY38">
-        <v>1.18</v>
-      </c>
-      <c r="AZ38">
-        <v>0</v>
-      </c>
-      <c r="BA38">
-        <v>0</v>
-      </c>
-      <c r="BB38">
-        <v>1.62</v>
-      </c>
-      <c r="BC38">
-        <v>3</v>
-      </c>
-      <c r="BD38" s="3">
+        <v>267</v>
+      </c>
+      <c r="AL38" s="3">
         <v>45754.64583333334</v>
       </c>
     </row>
-    <row r="39" spans="1:56">
+    <row r="39" spans="1:38">
       <c r="A39" s="2">
         <v>45754</v>
       </c>
       <c r="B39" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C39" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D39" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E39" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="F39" t="s">
+        <v>188</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39">
+        <v>2</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" t="s">
         <v>206</v>
       </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
-      <c r="I39">
-        <v>1</v>
-      </c>
-      <c r="J39">
-        <v>1</v>
-      </c>
-      <c r="K39" t="s">
-        <v>224</v>
-      </c>
       <c r="L39">
-        <v>2.7</v>
+        <v>1.43</v>
       </c>
       <c r="M39">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="N39">
-        <v>2.45</v>
+        <v>7.8</v>
       </c>
       <c r="O39">
-        <v>1.83</v>
+        <v>1.29</v>
       </c>
       <c r="P39">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q39">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="R39">
         <v>1.44</v>
@@ -7790,138 +5684,84 @@
         <v>2.63</v>
       </c>
       <c r="T39">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U39">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V39">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z39">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AA39">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AB39">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC39">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AD39">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AE39">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF39">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AG39">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AH39">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="AI39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ39" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="AK39" t="s">
-        <v>286</v>
-      </c>
-      <c r="AL39">
-        <v>1.35</v>
-      </c>
-      <c r="AM39">
-        <v>1.28</v>
-      </c>
-      <c r="AN39">
-        <v>1.45</v>
-      </c>
-      <c r="AO39">
-        <v>8</v>
-      </c>
-      <c r="AP39">
-        <v>1.4</v>
-      </c>
-      <c r="AQ39">
-        <v>1.75</v>
-      </c>
-      <c r="AR39">
-        <v>2.24</v>
-      </c>
-      <c r="AS39">
-        <v>3.05</v>
-      </c>
-      <c r="AT39">
-        <v>4.1</v>
-      </c>
-      <c r="AU39">
-        <v>2.56</v>
-      </c>
-      <c r="AV39">
-        <v>1.92</v>
-      </c>
-      <c r="AW39">
-        <v>1.52</v>
-      </c>
-      <c r="AX39">
-        <v>1.28</v>
-      </c>
-      <c r="AY39">
-        <v>1.18</v>
-      </c>
-      <c r="AZ39">
-        <v>0</v>
-      </c>
-      <c r="BA39">
-        <v>0</v>
-      </c>
-      <c r="BB39">
-        <v>1.83</v>
-      </c>
-      <c r="BC39">
-        <v>2.2</v>
-      </c>
-      <c r="BD39" s="3">
+        <v>268</v>
+      </c>
+      <c r="AL39" s="3">
         <v>45754.64583333334</v>
       </c>
     </row>
-    <row r="40" spans="1:56">
+    <row r="40" spans="1:38">
       <c r="A40" s="2">
         <v>45754</v>
       </c>
       <c r="B40" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C40" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="D40" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E40" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="F40" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -7930,168 +5770,114 @@
         <v>0</v>
       </c>
       <c r="J40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L40">
-        <v>2.96</v>
+        <v>2.25</v>
       </c>
       <c r="M40">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="N40">
-        <v>2.69</v>
+        <v>3.11</v>
       </c>
       <c r="O40">
+        <v>1.8</v>
+      </c>
+      <c r="P40">
+        <v>8</v>
+      </c>
+      <c r="Q40">
         <v>2.25</v>
       </c>
-      <c r="P40">
-        <v>6.75</v>
-      </c>
-      <c r="Q40">
-        <v>1.91</v>
-      </c>
       <c r="R40">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="S40">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="T40">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="U40">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V40">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W40">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
+        <v>1.07</v>
+      </c>
+      <c r="Y40">
+        <v>8</v>
+      </c>
+      <c r="Z40">
+        <v>1.33</v>
+      </c>
+      <c r="AA40">
+        <v>3.2</v>
+      </c>
+      <c r="AB40">
+        <v>1.92</v>
+      </c>
+      <c r="AC40">
+        <v>1.82</v>
+      </c>
+      <c r="AD40">
+        <v>3.45</v>
+      </c>
+      <c r="AE40">
+        <v>1.3</v>
+      </c>
+      <c r="AF40">
+        <v>1.73</v>
+      </c>
+      <c r="AG40">
+        <v>2</v>
+      </c>
+      <c r="AH40">
+        <v>6.5</v>
+      </c>
+      <c r="AI40">
         <v>1.1</v>
       </c>
-      <c r="Y40">
-        <v>6.5</v>
-      </c>
-      <c r="Z40">
-        <v>1.48</v>
-      </c>
-      <c r="AA40">
-        <v>2.6</v>
-      </c>
-      <c r="AB40">
-        <v>2.3</v>
-      </c>
-      <c r="AC40">
-        <v>1.57</v>
-      </c>
-      <c r="AD40">
-        <v>4.75</v>
-      </c>
-      <c r="AE40">
-        <v>1.18</v>
-      </c>
-      <c r="AF40">
-        <v>2</v>
-      </c>
-      <c r="AG40">
-        <v>1.75</v>
-      </c>
-      <c r="AH40">
-        <v>9.5</v>
-      </c>
-      <c r="AI40">
-        <v>1.05</v>
-      </c>
       <c r="AJ40" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="AK40" t="s">
-        <v>287</v>
-      </c>
-      <c r="AL40">
-        <v>1.47</v>
-      </c>
-      <c r="AM40">
-        <v>1.36</v>
-      </c>
-      <c r="AN40">
-        <v>1.41</v>
-      </c>
-      <c r="AO40">
-        <v>11</v>
-      </c>
-      <c r="AP40">
-        <v>1.42</v>
-      </c>
-      <c r="AQ40">
-        <v>1.78</v>
-      </c>
-      <c r="AR40">
-        <v>2.3</v>
-      </c>
-      <c r="AS40">
-        <v>3.08</v>
-      </c>
-      <c r="AT40">
-        <v>4.45</v>
-      </c>
-      <c r="AU40">
-        <v>2.57</v>
-      </c>
-      <c r="AV40">
-        <v>1.93</v>
-      </c>
-      <c r="AW40">
-        <v>1.52</v>
-      </c>
-      <c r="AX40">
-        <v>1.28</v>
-      </c>
-      <c r="AY40">
-        <v>1.14</v>
-      </c>
-      <c r="AZ40">
-        <v>0</v>
-      </c>
-      <c r="BA40">
-        <v>0</v>
-      </c>
-      <c r="BB40">
-        <v>2.25</v>
-      </c>
-      <c r="BC40">
-        <v>1.91</v>
-      </c>
-      <c r="BD40" s="3">
+        <v>269</v>
+      </c>
+      <c r="AL40" s="3">
         <v>45754.65625</v>
       </c>
     </row>
-    <row r="41" spans="1:56">
+    <row r="41" spans="1:38">
       <c r="A41" s="2">
         <v>45754</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C41" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="D41" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E41" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="F41" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="G41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -8100,165 +5886,111 @@
         <v>0</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L41">
+        <v>2.96</v>
+      </c>
+      <c r="M41">
+        <v>3.08</v>
+      </c>
+      <c r="N41">
+        <v>2.69</v>
+      </c>
+      <c r="O41">
         <v>2.25</v>
       </c>
-      <c r="M41">
-        <v>3.3</v>
-      </c>
-      <c r="N41">
-        <v>3.11</v>
-      </c>
-      <c r="O41">
-        <v>1.8</v>
-      </c>
       <c r="P41">
-        <v>8</v>
+        <v>6.75</v>
       </c>
       <c r="Q41">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="R41">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="S41">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="T41">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="U41">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V41">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W41">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X41">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y41">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="Z41">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AA41">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AB41">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AC41">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AD41">
-        <v>3.45</v>
+        <v>4.75</v>
       </c>
       <c r="AE41">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AF41">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AG41">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH41">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="AI41">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AJ41" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="AK41" t="s">
-        <v>288</v>
-      </c>
-      <c r="AL41">
-        <v>1.36</v>
-      </c>
-      <c r="AM41">
-        <v>1.28</v>
-      </c>
-      <c r="AN41">
-        <v>1.55</v>
-      </c>
-      <c r="AO41">
-        <v>6</v>
-      </c>
-      <c r="AP41">
-        <v>1.45</v>
-      </c>
-      <c r="AQ41">
-        <v>1.74</v>
-      </c>
-      <c r="AR41">
-        <v>2.2</v>
-      </c>
-      <c r="AS41">
-        <v>2.88</v>
-      </c>
-      <c r="AT41">
-        <v>3.8</v>
-      </c>
-      <c r="AU41">
-        <v>2.55</v>
-      </c>
-      <c r="AV41">
-        <v>1.95</v>
-      </c>
-      <c r="AW41">
-        <v>1.58</v>
-      </c>
-      <c r="AX41">
-        <v>1.35</v>
-      </c>
-      <c r="AY41">
-        <v>1.22</v>
-      </c>
-      <c r="AZ41">
-        <v>0</v>
-      </c>
-      <c r="BA41">
-        <v>0</v>
-      </c>
-      <c r="BB41">
-        <v>1.8</v>
-      </c>
-      <c r="BC41">
-        <v>2.25</v>
-      </c>
-      <c r="BD41" s="3">
+        <v>270</v>
+      </c>
+      <c r="AL41" s="3">
         <v>45754.65625</v>
       </c>
     </row>
-    <row r="42" spans="1:56">
+    <row r="42" spans="1:38">
       <c r="A42" s="2">
         <v>45754</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C42" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="D42" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E42" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="F42" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -8273,7 +6005,7 @@
         <v>3</v>
       </c>
       <c r="K42" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L42">
         <v>5.8</v>
@@ -8348,87 +6080,33 @@
         <v>1.2</v>
       </c>
       <c r="AJ42" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="AK42" t="s">
-        <v>289</v>
-      </c>
-      <c r="AL42">
-        <v>2.5</v>
-      </c>
-      <c r="AM42">
-        <v>1.2</v>
-      </c>
-      <c r="AN42">
-        <v>1.13</v>
-      </c>
-      <c r="AO42">
-        <v>-1</v>
-      </c>
-      <c r="AP42">
-        <v>1.2</v>
-      </c>
-      <c r="AQ42">
-        <v>1.36</v>
-      </c>
-      <c r="AR42">
-        <v>1.58</v>
-      </c>
-      <c r="AS42">
-        <v>1.95</v>
-      </c>
-      <c r="AT42">
-        <v>2.43</v>
-      </c>
-      <c r="AU42">
-        <v>3.9</v>
-      </c>
-      <c r="AV42">
-        <v>2.8</v>
-      </c>
-      <c r="AW42">
-        <v>2.17</v>
-      </c>
-      <c r="AX42">
-        <v>1.75</v>
-      </c>
-      <c r="AY42">
-        <v>1.48</v>
-      </c>
-      <c r="AZ42">
-        <v>0</v>
-      </c>
-      <c r="BA42">
-        <v>0</v>
-      </c>
-      <c r="BB42">
-        <v>3.4</v>
-      </c>
-      <c r="BC42">
-        <v>1.33</v>
-      </c>
-      <c r="BD42" s="3">
+        <v>271</v>
+      </c>
+      <c r="AL42" s="3">
         <v>45754.66666666666</v>
       </c>
     </row>
-    <row r="43" spans="1:56">
+    <row r="43" spans="1:38">
       <c r="A43" s="2">
         <v>45754</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C43" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="D43" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E43" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="F43" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -8443,7 +6121,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L43">
         <v>2.7</v>
@@ -8518,87 +6196,33 @@
         <v>1.06</v>
       </c>
       <c r="AJ43" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="AK43" t="s">
-        <v>290</v>
-      </c>
-      <c r="AL43">
-        <v>1.43</v>
-      </c>
-      <c r="AM43">
-        <v>1.34</v>
-      </c>
-      <c r="AN43">
-        <v>1.47</v>
-      </c>
-      <c r="AO43">
-        <v>-1</v>
-      </c>
-      <c r="AP43">
-        <v>1.4</v>
-      </c>
-      <c r="AQ43">
-        <v>1.67</v>
-      </c>
-      <c r="AR43">
-        <v>2.08</v>
-      </c>
-      <c r="AS43">
-        <v>2.65</v>
-      </c>
-      <c r="AT43">
-        <v>3.55</v>
-      </c>
-      <c r="AU43">
-        <v>2.65</v>
-      </c>
-      <c r="AV43">
-        <v>2.04</v>
-      </c>
-      <c r="AW43">
-        <v>1.65</v>
-      </c>
-      <c r="AX43">
-        <v>1.4</v>
-      </c>
-      <c r="AY43">
-        <v>1.24</v>
-      </c>
-      <c r="AZ43">
-        <v>0</v>
-      </c>
-      <c r="BA43">
-        <v>0</v>
-      </c>
-      <c r="BB43">
-        <v>1.91</v>
-      </c>
-      <c r="BC43">
-        <v>2.2</v>
-      </c>
-      <c r="BD43" s="3">
+        <v>272</v>
+      </c>
+      <c r="AL43" s="3">
         <v>45754.66666666666</v>
       </c>
     </row>
-    <row r="44" spans="1:56">
+    <row r="44" spans="1:38">
       <c r="A44" s="2">
         <v>45754</v>
       </c>
       <c r="B44" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C44" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D44" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E44" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="F44" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -8613,7 +6237,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L44">
         <v>1.77</v>
@@ -8688,87 +6312,33 @@
         <v>1.04</v>
       </c>
       <c r="AJ44" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="AK44" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL44">
-        <v>1.21</v>
-      </c>
-      <c r="AM44">
-        <v>1.29</v>
-      </c>
-      <c r="AN44">
-        <v>1.93</v>
-      </c>
-      <c r="AO44">
-        <v>-1</v>
-      </c>
-      <c r="AP44">
-        <v>1.24</v>
-      </c>
-      <c r="AQ44">
-        <v>1.48</v>
-      </c>
-      <c r="AR44">
-        <v>1.85</v>
-      </c>
-      <c r="AS44">
-        <v>2.38</v>
-      </c>
-      <c r="AT44">
-        <v>3.14</v>
-      </c>
-      <c r="AU44">
-        <v>3.34</v>
-      </c>
-      <c r="AV44">
-        <v>2.4</v>
-      </c>
-      <c r="AW44">
-        <v>1.85</v>
-      </c>
-      <c r="AX44">
-        <v>1.49</v>
-      </c>
-      <c r="AY44">
-        <v>1.27</v>
-      </c>
-      <c r="AZ44">
-        <v>0</v>
-      </c>
-      <c r="BA44">
-        <v>0</v>
-      </c>
-      <c r="BB44">
-        <v>1.53</v>
-      </c>
-      <c r="BC44">
-        <v>2.88</v>
-      </c>
-      <c r="BD44" s="3">
+        <v>273</v>
+      </c>
+      <c r="AL44" s="3">
         <v>45754.67708333334</v>
       </c>
     </row>
-    <row r="45" spans="1:56">
+    <row r="45" spans="1:38">
       <c r="A45" s="2">
         <v>45754</v>
       </c>
       <c r="B45" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="D45" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E45" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="F45" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -8783,7 +6353,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L45">
         <v>2.19</v>
@@ -8858,87 +6428,33 @@
         <v>1.27</v>
       </c>
       <c r="AJ45" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="AK45" t="s">
-        <v>279</v>
-      </c>
-      <c r="AL45">
-        <v>1.36</v>
-      </c>
-      <c r="AM45">
-        <v>1.27</v>
-      </c>
-      <c r="AN45">
-        <v>1.68</v>
-      </c>
-      <c r="AO45">
-        <v>14</v>
-      </c>
-      <c r="AP45">
-        <v>1.08</v>
-      </c>
-      <c r="AQ45">
-        <v>1.17</v>
-      </c>
-      <c r="AR45">
-        <v>1.31</v>
-      </c>
-      <c r="AS45">
-        <v>1.54</v>
-      </c>
-      <c r="AT45">
-        <v>1.87</v>
-      </c>
-      <c r="AU45">
-        <v>6.15</v>
-      </c>
-      <c r="AV45">
-        <v>4.2</v>
-      </c>
-      <c r="AW45">
-        <v>3.05</v>
-      </c>
-      <c r="AX45">
-        <v>2.31</v>
-      </c>
-      <c r="AY45">
-        <v>1.87</v>
-      </c>
-      <c r="AZ45">
-        <v>0</v>
-      </c>
-      <c r="BA45">
-        <v>0</v>
-      </c>
-      <c r="BB45">
-        <v>1.67</v>
-      </c>
-      <c r="BC45">
-        <v>2.1</v>
-      </c>
-      <c r="BD45" s="3">
+        <v>258</v>
+      </c>
+      <c r="AL45" s="3">
         <v>45754.67708333334</v>
       </c>
     </row>
-    <row r="46" spans="1:56">
+    <row r="46" spans="1:38">
       <c r="A46" s="2">
         <v>45754</v>
       </c>
       <c r="B46" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C46" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="D46" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E46" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="F46" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -8953,7 +6469,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L46">
         <v>1.51</v>
@@ -9028,87 +6544,33 @@
         <v>0</v>
       </c>
       <c r="AJ46" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="AK46" t="s">
-        <v>254</v>
-      </c>
-      <c r="AL46">
-        <v>0</v>
-      </c>
-      <c r="AM46">
-        <v>0</v>
-      </c>
-      <c r="AN46">
-        <v>0</v>
-      </c>
-      <c r="AO46">
-        <v>-1</v>
-      </c>
-      <c r="AP46">
-        <v>0</v>
-      </c>
-      <c r="AQ46">
-        <v>0</v>
-      </c>
-      <c r="AR46">
-        <v>0</v>
-      </c>
-      <c r="AS46">
-        <v>0</v>
-      </c>
-      <c r="AT46">
-        <v>0</v>
-      </c>
-      <c r="AU46">
-        <v>0</v>
-      </c>
-      <c r="AV46">
-        <v>0</v>
-      </c>
-      <c r="AW46">
-        <v>0</v>
-      </c>
-      <c r="AX46">
-        <v>0</v>
-      </c>
-      <c r="AY46">
-        <v>0</v>
-      </c>
-      <c r="AZ46">
-        <v>0</v>
-      </c>
-      <c r="BA46">
-        <v>0</v>
-      </c>
-      <c r="BB46">
-        <v>1.36</v>
-      </c>
-      <c r="BC46">
-        <v>3.25</v>
-      </c>
-      <c r="BD46" s="3">
+        <v>236</v>
+      </c>
+      <c r="AL46" s="3">
         <v>45754.69791666666</v>
       </c>
     </row>
-    <row r="47" spans="1:56">
+    <row r="47" spans="1:38">
       <c r="A47" s="2">
         <v>45754</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C47" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="D47" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E47" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="F47" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="G47">
         <v>2</v>
@@ -9123,7 +6585,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L47">
         <v>3.14</v>
@@ -9198,427 +6660,265 @@
         <v>1.01</v>
       </c>
       <c r="AJ47" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="AK47" t="s">
-        <v>292</v>
-      </c>
-      <c r="AL47">
-        <v>1.45</v>
-      </c>
-      <c r="AM47">
-        <v>1.36</v>
-      </c>
-      <c r="AN47">
-        <v>1.33</v>
-      </c>
-      <c r="AO47">
-        <v>12</v>
-      </c>
-      <c r="AP47">
-        <v>1.6</v>
-      </c>
-      <c r="AQ47">
-        <v>2</v>
-      </c>
-      <c r="AR47">
-        <v>2.55</v>
-      </c>
-      <c r="AS47">
-        <v>3.4</v>
-      </c>
-      <c r="AT47">
-        <v>4.6</v>
-      </c>
-      <c r="AU47">
-        <v>2.17</v>
-      </c>
-      <c r="AV47">
-        <v>1.71</v>
-      </c>
-      <c r="AW47">
-        <v>1.44</v>
-      </c>
-      <c r="AX47">
-        <v>1.26</v>
-      </c>
-      <c r="AY47">
-        <v>1.15</v>
-      </c>
-      <c r="AZ47">
-        <v>0</v>
-      </c>
-      <c r="BA47">
-        <v>0</v>
-      </c>
-      <c r="BB47">
-        <v>2.4</v>
-      </c>
-      <c r="BC47">
-        <v>1.95</v>
-      </c>
-      <c r="BD47" s="3">
+        <v>274</v>
+      </c>
+      <c r="AL47" s="3">
         <v>45754.75</v>
       </c>
     </row>
-    <row r="48" spans="1:56">
+    <row r="48" spans="1:38">
       <c r="A48" s="2">
         <v>45754</v>
       </c>
       <c r="B48" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C48" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="D48" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="E48" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="F48" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="G48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48" t="s">
+        <v>206</v>
+      </c>
+      <c r="L48">
+        <v>2.15</v>
+      </c>
+      <c r="M48">
+        <v>3.2</v>
+      </c>
+      <c r="N48">
+        <v>3.2</v>
+      </c>
+      <c r="O48">
+        <v>1.83</v>
+      </c>
+      <c r="P48">
+        <v>7</v>
+      </c>
+      <c r="Q48">
+        <v>2.5</v>
+      </c>
+      <c r="R48">
+        <v>1.53</v>
+      </c>
+      <c r="S48">
+        <v>2.38</v>
+      </c>
+      <c r="T48">
+        <v>3.45</v>
+      </c>
+      <c r="U48">
+        <v>1.25</v>
+      </c>
+      <c r="V48">
+        <v>9.5</v>
+      </c>
+      <c r="W48">
+        <v>1.04</v>
+      </c>
+      <c r="X48">
+        <v>1.02</v>
+      </c>
+      <c r="Y48">
+        <v>7.7</v>
+      </c>
+      <c r="Z48">
+        <v>1.45</v>
+      </c>
+      <c r="AA48">
+        <v>2.6</v>
+      </c>
+      <c r="AB48">
+        <v>2.1</v>
+      </c>
+      <c r="AC48">
+        <v>1.61</v>
+      </c>
+      <c r="AD48">
+        <v>4.5</v>
+      </c>
+      <c r="AE48">
+        <v>1.18</v>
+      </c>
+      <c r="AF48">
         <v>2</v>
       </c>
-      <c r="I48">
-        <v>1</v>
-      </c>
-      <c r="J48">
-        <v>1</v>
-      </c>
-      <c r="K48" t="s">
-        <v>224</v>
-      </c>
-      <c r="L48">
-        <v>1.72</v>
-      </c>
-      <c r="M48">
-        <v>3.66</v>
-      </c>
-      <c r="N48">
-        <v>4.6</v>
-      </c>
-      <c r="O48">
-        <v>1.5</v>
-      </c>
-      <c r="P48">
-        <v>8.25</v>
-      </c>
-      <c r="Q48">
-        <v>2.88</v>
-      </c>
-      <c r="R48">
-        <v>1.4</v>
-      </c>
-      <c r="S48">
-        <v>2.75</v>
-      </c>
-      <c r="T48">
-        <v>2.75</v>
-      </c>
-      <c r="U48">
-        <v>1.4</v>
-      </c>
-      <c r="V48">
-        <v>8</v>
-      </c>
-      <c r="W48">
-        <v>1.08</v>
-      </c>
-      <c r="X48">
-        <v>1.01</v>
-      </c>
-      <c r="Y48">
-        <v>8.9</v>
-      </c>
-      <c r="Z48">
-        <v>1.28</v>
-      </c>
-      <c r="AA48">
-        <v>3.08</v>
-      </c>
-      <c r="AB48">
-        <v>1.89</v>
-      </c>
-      <c r="AC48">
-        <v>1.85</v>
-      </c>
-      <c r="AD48">
-        <v>3.52</v>
-      </c>
-      <c r="AE48">
-        <v>1.22</v>
-      </c>
-      <c r="AF48">
-        <v>1.83</v>
-      </c>
       <c r="AG48">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AH48">
-        <v>7.1</v>
+        <v>10</v>
       </c>
       <c r="AI48">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ48" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="AK48" t="s">
-        <v>293</v>
-      </c>
-      <c r="AL48">
-        <v>1.21</v>
-      </c>
-      <c r="AM48">
-        <v>1.28</v>
-      </c>
-      <c r="AN48">
-        <v>1.93</v>
-      </c>
-      <c r="AO48">
-        <v>11</v>
-      </c>
-      <c r="AP48">
-        <v>1.18</v>
-      </c>
-      <c r="AQ48">
-        <v>1.26</v>
-      </c>
-      <c r="AR48">
-        <v>1.47</v>
-      </c>
-      <c r="AS48">
-        <v>1.82</v>
-      </c>
-      <c r="AT48">
-        <v>2.35</v>
-      </c>
-      <c r="AU48">
-        <v>4.1</v>
-      </c>
-      <c r="AV48">
-        <v>3.4</v>
-      </c>
-      <c r="AW48">
-        <v>2.37</v>
-      </c>
-      <c r="AX48">
-        <v>1.83</v>
-      </c>
-      <c r="AY48">
-        <v>1.49</v>
-      </c>
-      <c r="AZ48">
-        <v>0</v>
-      </c>
-      <c r="BA48">
-        <v>0</v>
-      </c>
-      <c r="BB48">
-        <v>1.5</v>
-      </c>
-      <c r="BC48">
-        <v>2.88</v>
-      </c>
-      <c r="BD48" s="3">
+        <v>208</v>
+      </c>
+      <c r="AL48" s="3">
         <v>45754.79166666666</v>
       </c>
     </row>
-    <row r="49" spans="1:56">
+    <row r="49" spans="1:38">
       <c r="A49" s="2">
         <v>45754</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C49" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D49" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="E49" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="F49" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I49">
         <v>1</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L49">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="M49">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="N49">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="O49">
+        <v>1.5</v>
+      </c>
+      <c r="P49">
+        <v>8.25</v>
+      </c>
+      <c r="Q49">
+        <v>2.88</v>
+      </c>
+      <c r="R49">
+        <v>1.4</v>
+      </c>
+      <c r="S49">
+        <v>2.75</v>
+      </c>
+      <c r="T49">
+        <v>2.75</v>
+      </c>
+      <c r="U49">
+        <v>1.4</v>
+      </c>
+      <c r="V49">
+        <v>8</v>
+      </c>
+      <c r="W49">
+        <v>1.08</v>
+      </c>
+      <c r="X49">
+        <v>1.01</v>
+      </c>
+      <c r="Y49">
+        <v>8.9</v>
+      </c>
+      <c r="Z49">
+        <v>1.28</v>
+      </c>
+      <c r="AA49">
+        <v>3.08</v>
+      </c>
+      <c r="AB49">
+        <v>1.89</v>
+      </c>
+      <c r="AC49">
+        <v>1.85</v>
+      </c>
+      <c r="AD49">
+        <v>3.52</v>
+      </c>
+      <c r="AE49">
+        <v>1.22</v>
+      </c>
+      <c r="AF49">
         <v>1.83</v>
       </c>
-      <c r="P49">
-        <v>7</v>
-      </c>
-      <c r="Q49">
-        <v>2.5</v>
-      </c>
-      <c r="R49">
-        <v>1.53</v>
-      </c>
-      <c r="S49">
-        <v>2.38</v>
-      </c>
-      <c r="T49">
-        <v>3.45</v>
-      </c>
-      <c r="U49">
-        <v>1.25</v>
-      </c>
-      <c r="V49">
-        <v>9.5</v>
-      </c>
-      <c r="W49">
+      <c r="AG49">
+        <v>1.83</v>
+      </c>
+      <c r="AH49">
+        <v>7.1</v>
+      </c>
+      <c r="AI49">
         <v>1.04</v>
       </c>
-      <c r="X49">
-        <v>1.02</v>
-      </c>
-      <c r="Y49">
-        <v>7.7</v>
-      </c>
-      <c r="Z49">
-        <v>1.45</v>
-      </c>
-      <c r="AA49">
-        <v>2.6</v>
-      </c>
-      <c r="AB49">
-        <v>2.1</v>
-      </c>
-      <c r="AC49">
-        <v>1.61</v>
-      </c>
-      <c r="AD49">
-        <v>4.5</v>
-      </c>
-      <c r="AE49">
-        <v>1.18</v>
-      </c>
-      <c r="AF49">
-        <v>2</v>
-      </c>
-      <c r="AG49">
-        <v>1.67</v>
-      </c>
-      <c r="AH49">
-        <v>10</v>
-      </c>
-      <c r="AI49">
-        <v>1.05</v>
-      </c>
       <c r="AJ49" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="AK49" t="s">
-        <v>226</v>
-      </c>
-      <c r="AL49">
-        <v>1.25</v>
-      </c>
-      <c r="AM49">
-        <v>1.3</v>
-      </c>
-      <c r="AN49">
-        <v>1.65</v>
-      </c>
-      <c r="AO49">
-        <v>3</v>
-      </c>
-      <c r="AP49">
-        <v>0</v>
-      </c>
-      <c r="AQ49">
-        <v>1.9</v>
-      </c>
-      <c r="AR49">
-        <v>0</v>
-      </c>
-      <c r="AS49">
-        <v>0</v>
-      </c>
-      <c r="AT49">
-        <v>0</v>
-      </c>
-      <c r="AU49">
-        <v>0</v>
-      </c>
-      <c r="AV49">
-        <v>1.9</v>
-      </c>
-      <c r="AW49">
-        <v>0</v>
-      </c>
-      <c r="AX49">
-        <v>0</v>
-      </c>
-      <c r="AY49">
-        <v>0</v>
-      </c>
-      <c r="AZ49">
-        <v>0</v>
-      </c>
-      <c r="BA49">
-        <v>0</v>
-      </c>
-      <c r="BB49">
-        <v>1.83</v>
-      </c>
-      <c r="BC49">
-        <v>2.5</v>
-      </c>
-      <c r="BD49" s="3">
+        <v>275</v>
+      </c>
+      <c r="AL49" s="3">
         <v>45754.79166666666</v>
       </c>
     </row>
-    <row r="50" spans="1:56">
+    <row r="50" spans="1:38">
       <c r="A50" s="2">
         <v>45754</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C50" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="D50" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E50" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="F50" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="G50">
         <v>2</v>
@@ -9633,7 +6933,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L50">
         <v>1.69</v>
@@ -9708,87 +7008,33 @@
         <v>1.01</v>
       </c>
       <c r="AJ50" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="AK50" t="s">
-        <v>226</v>
-      </c>
-      <c r="AL50">
-        <v>1.1</v>
-      </c>
-      <c r="AM50">
-        <v>1.28</v>
-      </c>
-      <c r="AN50">
-        <v>2.06</v>
-      </c>
-      <c r="AO50">
-        <v>6</v>
-      </c>
-      <c r="AP50">
-        <v>1.49</v>
-      </c>
-      <c r="AQ50">
-        <v>1.81</v>
-      </c>
-      <c r="AR50">
-        <v>2.3</v>
-      </c>
-      <c r="AS50">
-        <v>3</v>
-      </c>
-      <c r="AT50">
-        <v>4.1</v>
-      </c>
-      <c r="AU50">
-        <v>2.4</v>
-      </c>
-      <c r="AV50">
-        <v>1.88</v>
-      </c>
-      <c r="AW50">
-        <v>1.54</v>
-      </c>
-      <c r="AX50">
-        <v>1.32</v>
-      </c>
-      <c r="AY50">
-        <v>1.19</v>
-      </c>
-      <c r="AZ50">
-        <v>0</v>
-      </c>
-      <c r="BA50">
-        <v>0</v>
-      </c>
-      <c r="BB50">
-        <v>1.62</v>
-      </c>
-      <c r="BC50">
-        <v>3.1</v>
-      </c>
-      <c r="BD50" s="3">
+        <v>208</v>
+      </c>
+      <c r="AL50" s="3">
         <v>45754.79166666666</v>
       </c>
     </row>
-    <row r="51" spans="1:56">
+    <row r="51" spans="1:38">
       <c r="A51" s="2">
         <v>45754</v>
       </c>
       <c r="B51" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C51" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="D51" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E51" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="F51" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -9803,7 +7049,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L51">
         <v>3.45</v>
@@ -9878,87 +7124,33 @@
         <v>1.07</v>
       </c>
       <c r="AJ51" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="AK51" t="s">
-        <v>226</v>
-      </c>
-      <c r="AL51">
-        <v>1.29</v>
-      </c>
-      <c r="AM51">
-        <v>1.3</v>
-      </c>
-      <c r="AN51">
-        <v>1.72</v>
-      </c>
-      <c r="AO51">
-        <v>-1</v>
-      </c>
-      <c r="AP51">
-        <v>1.3</v>
-      </c>
-      <c r="AQ51">
-        <v>1.7</v>
-      </c>
-      <c r="AR51">
-        <v>1.89</v>
-      </c>
-      <c r="AS51">
-        <v>2.35</v>
-      </c>
-      <c r="AT51">
-        <v>3.05</v>
-      </c>
-      <c r="AU51">
-        <v>3.05</v>
-      </c>
-      <c r="AV51">
-        <v>2.05</v>
-      </c>
-      <c r="AW51">
-        <v>1.8</v>
-      </c>
-      <c r="AX51">
-        <v>1.5</v>
-      </c>
-      <c r="AY51">
-        <v>1.32</v>
-      </c>
-      <c r="AZ51">
-        <v>0</v>
-      </c>
-      <c r="BA51">
-        <v>0</v>
-      </c>
-      <c r="BB51">
-        <v>1.75</v>
-      </c>
-      <c r="BC51">
-        <v>2.4</v>
-      </c>
-      <c r="BD51" s="3">
+        <v>208</v>
+      </c>
+      <c r="AL51" s="3">
         <v>45754.8125</v>
       </c>
     </row>
-    <row r="52" spans="1:56">
+    <row r="52" spans="1:38">
       <c r="A52" s="2">
         <v>45754</v>
       </c>
       <c r="B52" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="C52" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="D52" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E52" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="F52" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="G52">
         <v>3</v>
@@ -9973,7 +7165,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L52">
         <v>1.98</v>
@@ -10048,427 +7240,265 @@
         <v>1.01</v>
       </c>
       <c r="AJ52" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="AK52" t="s">
-        <v>294</v>
-      </c>
-      <c r="AL52">
-        <v>1.17</v>
-      </c>
-      <c r="AM52">
-        <v>1.33</v>
-      </c>
-      <c r="AN52">
-        <v>1.76</v>
-      </c>
-      <c r="AO52">
-        <v>7</v>
-      </c>
-      <c r="AP52">
-        <v>1.63</v>
-      </c>
-      <c r="AQ52">
-        <v>2.02</v>
-      </c>
-      <c r="AR52">
-        <v>2.65</v>
-      </c>
-      <c r="AS52">
-        <v>3.55</v>
-      </c>
-      <c r="AT52">
-        <v>4.8</v>
-      </c>
-      <c r="AU52">
-        <v>2.15</v>
-      </c>
-      <c r="AV52">
-        <v>1.7</v>
-      </c>
-      <c r="AW52">
-        <v>1.42</v>
-      </c>
-      <c r="AX52">
-        <v>1.24</v>
-      </c>
-      <c r="AY52">
-        <v>1.14</v>
-      </c>
-      <c r="AZ52">
-        <v>0</v>
-      </c>
-      <c r="BA52">
-        <v>0</v>
-      </c>
-      <c r="BB52">
-        <v>1.62</v>
-      </c>
-      <c r="BC52">
-        <v>3.1</v>
-      </c>
-      <c r="BD52" s="3">
+        <v>276</v>
+      </c>
+      <c r="AL52" s="3">
         <v>45754.85416666666</v>
       </c>
     </row>
-    <row r="53" spans="1:56">
+    <row r="53" spans="1:38">
       <c r="A53" s="2">
         <v>45754</v>
       </c>
       <c r="B53" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="C53" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D53" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E53" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="F53" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H53">
         <v>2</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L53">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="M53">
+        <v>3</v>
+      </c>
+      <c r="N53">
         <v>3.2</v>
       </c>
-      <c r="N53">
-        <v>4.2</v>
-      </c>
       <c r="O53">
+        <v>1.83</v>
+      </c>
+      <c r="P53">
+        <v>6</v>
+      </c>
+      <c r="Q53">
+        <v>2.4</v>
+      </c>
+      <c r="R53">
         <v>1.62</v>
       </c>
-      <c r="P53">
-        <v>6.75</v>
-      </c>
-      <c r="Q53">
-        <v>2.75</v>
-      </c>
-      <c r="R53">
-        <v>1.57</v>
-      </c>
       <c r="S53">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="T53">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U53">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V53">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W53">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X53">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y53">
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="Z53">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AA53">
-        <v>2.71</v>
+        <v>2.3</v>
       </c>
       <c r="AB53">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AC53">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AD53">
-        <v>4.15</v>
+        <v>5.5</v>
       </c>
       <c r="AE53">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF53">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG53">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH53">
-        <v>8.1</v>
+        <v>10</v>
       </c>
       <c r="AI53">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AJ53" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="AK53" t="s">
-        <v>295</v>
-      </c>
-      <c r="AL53">
-        <v>1.24</v>
-      </c>
-      <c r="AM53">
-        <v>1.32</v>
-      </c>
-      <c r="AN53">
-        <v>1.78</v>
-      </c>
-      <c r="AO53">
-        <v>-1</v>
-      </c>
-      <c r="AP53">
-        <v>1.48</v>
-      </c>
-      <c r="AQ53">
-        <v>1.8</v>
-      </c>
-      <c r="AR53">
-        <v>2.3</v>
-      </c>
-      <c r="AS53">
-        <v>3</v>
-      </c>
-      <c r="AT53">
-        <v>4</v>
-      </c>
-      <c r="AU53">
-        <v>2.43</v>
-      </c>
-      <c r="AV53">
-        <v>1.89</v>
-      </c>
-      <c r="AW53">
-        <v>1.53</v>
-      </c>
-      <c r="AX53">
-        <v>1.32</v>
-      </c>
-      <c r="AY53">
-        <v>1.18</v>
-      </c>
-      <c r="AZ53">
-        <v>0</v>
-      </c>
-      <c r="BA53">
-        <v>0</v>
-      </c>
-      <c r="BB53">
-        <v>1.62</v>
-      </c>
-      <c r="BC53">
-        <v>2.75</v>
-      </c>
-      <c r="BD53" s="3">
+        <v>277</v>
+      </c>
+      <c r="AL53" s="3">
         <v>45754.875</v>
       </c>
     </row>
-    <row r="54" spans="1:56">
+    <row r="54" spans="1:38">
       <c r="A54" s="2">
         <v>45754</v>
       </c>
       <c r="B54" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="C54" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D54" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E54" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="F54" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H54">
         <v>2</v>
       </c>
       <c r="I54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L54">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="M54">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N54">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="O54">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="P54">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="Q54">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="R54">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S54">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="T54">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U54">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V54">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W54">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X54">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Y54">
-        <v>6.25</v>
+        <v>6.75</v>
       </c>
       <c r="Z54">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AA54">
-        <v>2.3</v>
+        <v>2.71</v>
       </c>
       <c r="AB54">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AC54">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AD54">
-        <v>5.5</v>
+        <v>4.15</v>
       </c>
       <c r="AE54">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF54">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG54">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH54">
-        <v>10</v>
+        <v>8.1</v>
       </c>
       <c r="AI54">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AJ54" t="s">
-        <v>262</v>
+        <v>208</v>
       </c>
       <c r="AK54" t="s">
-        <v>296</v>
-      </c>
-      <c r="AL54">
-        <v>1.34</v>
-      </c>
-      <c r="AM54">
-        <v>1.36</v>
-      </c>
-      <c r="AN54">
-        <v>1.55</v>
-      </c>
-      <c r="AO54">
-        <v>-1</v>
-      </c>
-      <c r="AP54">
-        <v>1.28</v>
-      </c>
-      <c r="AQ54">
-        <v>1.52</v>
-      </c>
-      <c r="AR54">
-        <v>1.8</v>
-      </c>
-      <c r="AS54">
-        <v>2.38</v>
-      </c>
-      <c r="AT54">
-        <v>3.12</v>
-      </c>
-      <c r="AU54">
-        <v>3.25</v>
-      </c>
-      <c r="AV54">
-        <v>2.37</v>
-      </c>
-      <c r="AW54">
-        <v>1.91</v>
-      </c>
-      <c r="AX54">
-        <v>1.54</v>
-      </c>
-      <c r="AY54">
-        <v>1.31</v>
-      </c>
-      <c r="AZ54">
-        <v>0</v>
-      </c>
-      <c r="BA54">
-        <v>0</v>
-      </c>
-      <c r="BB54">
-        <v>1.83</v>
-      </c>
-      <c r="BC54">
-        <v>2.4</v>
-      </c>
-      <c r="BD54" s="3">
+        <v>278</v>
+      </c>
+      <c r="AL54" s="3">
         <v>45754.875</v>
       </c>
     </row>
-    <row r="55" spans="1:56">
+    <row r="55" spans="1:38">
       <c r="A55" s="2">
         <v>45754</v>
       </c>
       <c r="B55" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="D55" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E55" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="F55" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="G55">
         <v>3</v>
@@ -10483,7 +7513,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L55">
         <v>1.98</v>
@@ -10558,87 +7588,33 @@
         <v>1.01</v>
       </c>
       <c r="AJ55" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="AK55" t="s">
-        <v>226</v>
-      </c>
-      <c r="AL55">
-        <v>1.21</v>
-      </c>
-      <c r="AM55">
-        <v>1.33</v>
-      </c>
-      <c r="AN55">
-        <v>1.69</v>
-      </c>
-      <c r="AO55">
-        <v>5</v>
-      </c>
-      <c r="AP55">
-        <v>1.75</v>
-      </c>
-      <c r="AQ55">
-        <v>2.23</v>
-      </c>
-      <c r="AR55">
-        <v>2.95</v>
-      </c>
-      <c r="AS55">
-        <v>4</v>
-      </c>
-      <c r="AT55">
-        <v>5.4</v>
-      </c>
-      <c r="AU55">
-        <v>1.95</v>
-      </c>
-      <c r="AV55">
-        <v>1.57</v>
-      </c>
-      <c r="AW55">
-        <v>1.33</v>
-      </c>
-      <c r="AX55">
-        <v>1.2</v>
-      </c>
-      <c r="AY55">
-        <v>1.1</v>
-      </c>
-      <c r="AZ55">
-        <v>0</v>
-      </c>
-      <c r="BA55">
-        <v>0</v>
-      </c>
-      <c r="BB55">
-        <v>1.73</v>
-      </c>
-      <c r="BC55">
-        <v>3</v>
-      </c>
-      <c r="BD55" s="3">
+        <v>208</v>
+      </c>
+      <c r="AL55" s="3">
         <v>45754.88194444445</v>
       </c>
     </row>
-    <row r="56" spans="1:56">
+    <row r="56" spans="1:38">
       <c r="A56" s="2">
         <v>45754</v>
       </c>
       <c r="B56" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C56" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="D56" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E56" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="F56" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -10653,7 +7629,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="L56">
         <v>1.55</v>
@@ -10728,66 +7704,12 @@
         <v>1.15</v>
       </c>
       <c r="AJ56" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="AK56" t="s">
-        <v>226</v>
-      </c>
-      <c r="AL56">
-        <v>1.15</v>
-      </c>
-      <c r="AM56">
-        <v>1.21</v>
-      </c>
-      <c r="AN56">
-        <v>2.35</v>
-      </c>
-      <c r="AO56">
-        <v>9</v>
-      </c>
-      <c r="AP56">
-        <v>0</v>
-      </c>
-      <c r="AQ56">
-        <v>0</v>
-      </c>
-      <c r="AR56">
-        <v>0</v>
-      </c>
-      <c r="AS56">
-        <v>0</v>
-      </c>
-      <c r="AT56">
-        <v>0</v>
-      </c>
-      <c r="AU56">
-        <v>0</v>
-      </c>
-      <c r="AV56">
-        <v>0</v>
-      </c>
-      <c r="AW56">
-        <v>0</v>
-      </c>
-      <c r="AX56">
-        <v>0</v>
-      </c>
-      <c r="AY56">
-        <v>0</v>
-      </c>
-      <c r="AZ56">
-        <v>0</v>
-      </c>
-      <c r="BA56">
-        <v>0</v>
-      </c>
-      <c r="BB56">
-        <v>1.4</v>
-      </c>
-      <c r="BC56">
-        <v>3.2</v>
-      </c>
-      <c r="BD56" s="3">
+        <v>208</v>
+      </c>
+      <c r="AL56" s="3">
         <v>45754.90625</v>
       </c>
     </row>

--- a/jogos_2025-04-07.xlsx
+++ b/jogos_2025-04-07.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.71</v>
+        <v>2.14</v>
       </c>
       <c r="M6" t="n">
-        <v>3.55</v>
+        <v>3.41</v>
       </c>
       <c r="N6" t="n">
-        <v>4.9</v>
+        <v>3.23</v>
       </c>
       <c r="O6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y6" t="n">
         <v>2.1</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>6</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U6" t="n">
+      <c r="Z6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['7', '32']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
         <v>1.35</v>
       </c>
-      <c r="V6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['42']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['71']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AH6" t="n">
-        <v>2.32</v>
+        <v>1.57</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45754.47916666666</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,109 +1288,109 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y7" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Z7" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.87</v>
+        <v>3.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['7', '32']</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.57</v>
+        <v>2.32</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45754.47916666666</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,19 +1417,19 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sigma Olomouc II</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.01</v>
+        <v>2.26</v>
       </c>
       <c r="M8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N8" t="n">
         <v>3.31</v>
       </c>
-      <c r="N8" t="n">
-        <v>3.32</v>
-      </c>
       <c r="O8" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="R8" t="n">
         <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>3.42</v>
+        <v>2.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="Z8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI8" t="n">
         <v>1.82</v>
       </c>
-      <c r="AA8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>['52', '74', '81']</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ8" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45754.5</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Sigma Olomouc II</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>3.31</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="O9" t="n">
         <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="T9" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="X9" t="n">
-        <v>2.37</v>
+        <v>3.42</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.8</v>
+        <v>2.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
+          <t>['52', '74', '81']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['60']</t>
-        </is>
-      </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
         <v>1.75</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45754.5</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,16 +1675,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -1701,65 +1701,65 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.74</v>
+        <v>4.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="S10" t="n">
-        <v>2.73</v>
+        <v>2.25</v>
       </c>
       <c r="T10" t="n">
-        <v>3.04</v>
+        <v>3.75</v>
       </c>
       <c r="U10" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X10" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y10" t="n">
         <v>2.4</v>
       </c>
-      <c r="Y10" t="n">
-        <v>2.09</v>
-      </c>
       <c r="Z10" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.18</v>
+        <v>2.88</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45754.5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mladost Lučani</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>7.1</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>3.99</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>1.47</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['21', '33', '90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45754.54166666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,22 +1933,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.91</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '60', '73']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['12', '71']</t>
+          <t>['45+7', '68', '90+4']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AI12" t="n">
         <v>1.62</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45754.54166666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,65 +2088,65 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.76</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.44</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.33</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="X13" t="n">
-        <v>2.98</v>
+        <v>3.86</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Z13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45754.54166666666</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,109 +2191,109 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O14" t="n">
         <v>3</v>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N14" t="n">
-        <v>7</v>
-      </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['38', '76']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI14" t="n">
         <v>1.83</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['2', '13', '45+3']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>3.85</v>
+        <v>2.2</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45754.54166666666</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Mladost Lučani</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.55</v>
+        <v>7.1</v>
       </c>
       <c r="M15" t="n">
-        <v>3.76</v>
+        <v>3.99</v>
       </c>
       <c r="N15" t="n">
-        <v>6.3</v>
+        <v>1.47</v>
       </c>
       <c r="O15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['32']</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '33', '90+2']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45754.54166666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>3</v>
       </c>
       <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.92</v>
+        <v>1.36</v>
       </c>
       <c r="M16" t="n">
-        <v>3.39</v>
+        <v>4.6</v>
       </c>
       <c r="N16" t="n">
-        <v>3.93</v>
+        <v>7</v>
       </c>
       <c r="O16" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
-        <v>3.28</v>
+        <v>4.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.04</v>
+        <v>2.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['14', '60', '73']</t>
+          <t>['2', '13', '45+3']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['45+7', '68', '90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.79</v>
+        <v>3.1</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.6</v>
+        <v>3.85</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45754.54166666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="M17" t="n">
-        <v>3.29</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q17" t="n">
         <v>4.2</v>
       </c>
-      <c r="O17" t="n">
-        <v>3</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.4</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
         <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
-        <v>3.04</v>
+        <v>4.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.28</v>
+        <v>2.68</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2667,20 +2667,20 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['38', '76']</t>
+          <t>['12', '71']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45754.54166666666</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.6</v>
+        <v>3.15</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>3.32</v>
       </c>
       <c r="N19" t="n">
-        <v>1.56</v>
+        <v>2.18</v>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD19" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['90']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI19" t="n">
         <v>2.25</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['90+1']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['39', '82', '90+5']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>3</v>
-      </c>
       <c r="AJ19" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45754.58333333334</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="M20" t="n">
-        <v>3.84</v>
+        <v>3.99</v>
       </c>
       <c r="N20" t="n">
-        <v>1.59</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U20" t="n">
         <v>1.4</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T20" t="n">
+      <c r="V20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AA20" t="n">
         <v>3</v>
       </c>
-      <c r="U20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AB20" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3054,20 +3054,20 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="AG20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH20" t="n">
         <v>2.1</v>
       </c>
-      <c r="AH20" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AI20" t="n">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.44</v>
+        <v>2.88</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45754.58333333334</v>
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="N21" t="n">
-        <v>3.27</v>
+        <v>3.16</v>
       </c>
       <c r="O21" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
         <v>2.9</v>
       </c>
       <c r="T21" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.28</v>
       </c>
-      <c r="X21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AC21" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45754.58333333334</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3238,94 +3238,94 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="M22" t="n">
-        <v>3.32</v>
+        <v>3.84</v>
       </c>
       <c r="N22" t="n">
-        <v>2.18</v>
+        <v>1.59</v>
       </c>
       <c r="O22" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="P22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
         <v>2.75</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T22" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V22" t="n">
         <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X22" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="Z22" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>['14']</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['90']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45754.58333333334</v>
@@ -3342,119 +3342,119 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD23" t="n">
         <v>2</v>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="M23" t="n">
-        <v>4</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '50']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['17', '82']</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45754.58333333334</v>
@@ -3471,97 +3471,97 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3570,20 +3570,20 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['29']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45754.58333333334</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,16 +3610,16 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="M25" t="n">
-        <v>3.99</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="O25" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="T25" t="n">
-        <v>2.75</v>
+        <v>3.21</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="V25" t="n">
         <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="X25" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.96</v>
+        <v>1.61</v>
       </c>
       <c r="AA25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AC25" t="n">
         <v>1.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AH25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>2.88</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45754.58333333334</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,109 +3739,109 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="I26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.34</v>
+        <v>5.6</v>
       </c>
       <c r="M26" t="n">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.03</v>
+        <v>1.56</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="R26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U26" t="n">
         <v>1.4</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T26" t="n">
+      <c r="V26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['90+1']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['39', '82', '90+5']</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI26" t="n">
         <v>3</v>
       </c>
-      <c r="U26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>['13', '50']</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>['73']</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ26" t="n">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45754.58333333334</v>
@@ -4374,35 +4374,35 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="M31" t="n">
-        <v>5.9</v>
+        <v>4.75</v>
       </c>
       <c r="N31" t="n">
-        <v>7.5</v>
+        <v>4.75</v>
       </c>
       <c r="O31" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="R31" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="V31" t="n">
         <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X31" t="n">
-        <v>6.35</v>
+        <v>6.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['49', '79']</t>
+          <t>['52', '56']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '72']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AJ31" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45754.625</v>
@@ -4503,32 +4503,32 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="M32" t="n">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="N32" t="n">
-        <v>1.65</v>
+        <v>7.5</v>
       </c>
       <c r="O32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S32" t="n">
         <v>4.33</v>
       </c>
-      <c r="P32" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.61</v>
-      </c>
       <c r="T32" t="n">
-        <v>2.94</v>
+        <v>1.91</v>
       </c>
       <c r="U32" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="V32" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.36</v>
+        <v>1.06</v>
       </c>
       <c r="X32" t="n">
-        <v>2.9</v>
+        <v>6.35</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.15</v>
+        <v>1.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.6</v>
+        <v>3.21</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['49', '79']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI32" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>['31', '41', '62']</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AJ32" t="n">
-        <v>1.62</v>
+        <v>3.75</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45754.625</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G33" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
         <v>2</v>
       </c>
-      <c r="H33" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.55</v>
+        <v>4.5</v>
       </c>
       <c r="M33" t="n">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="N33" t="n">
-        <v>4.75</v>
+        <v>1.65</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>4.33</v>
       </c>
       <c r="P33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['31', '41', '62']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI33" t="n">
         <v>2.63</v>
       </c>
-      <c r="Q33" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S33" t="n">
-        <v>4</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['52', '56']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['14', '72']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AJ33" t="n">
-        <v>2.75</v>
+        <v>1.62</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45754.625</v>
@@ -6567,35 +6567,35 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
         <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="N48" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="O48" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="P48" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="R48" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="S48" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="T48" t="n">
-        <v>3.45</v>
+        <v>2.75</v>
       </c>
       <c r="U48" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="V48" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W48" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="X48" t="n">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AA48" t="n">
-        <v>4.5</v>
+        <v>3.52</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC48" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>['31', '47', '80']</t>
+          <t>['43', '69', '79', '90+3']</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '88']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45754.79166666666</v>
@@ -6696,35 +6696,35 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="M49" t="n">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="N49" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="O49" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S49" t="n">
         <v>2.38</v>
       </c>
-      <c r="P49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>5</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T49" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="U49" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V49" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W49" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="X49" t="n">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AA49" t="n">
-        <v>3.52</v>
+        <v>4.5</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>['31', '47', '80']</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI49" t="n">
         <v>1.83</v>
       </c>
-      <c r="AD49" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>['43', '69', '79', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>['9', '88']</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AJ49" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45754.79166666666</v>
